--- a/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,150 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2658500</v>
+        <v>2318500</v>
       </c>
       <c r="E8" s="3">
-        <v>3148800</v>
+        <v>2605300</v>
       </c>
       <c r="F8" s="3">
-        <v>3416500</v>
+        <v>3085800</v>
       </c>
       <c r="G8" s="3">
-        <v>3030200</v>
+        <v>3348200</v>
       </c>
       <c r="H8" s="3">
-        <v>3892800</v>
+        <v>2969600</v>
       </c>
       <c r="I8" s="3">
-        <v>3166400</v>
+        <v>3814900</v>
       </c>
       <c r="J8" s="3">
+        <v>3103100</v>
+      </c>
+      <c r="K8" s="3">
         <v>2279000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2378200</v>
+        <v>2135100</v>
       </c>
       <c r="E9" s="3">
-        <v>2212100</v>
+        <v>2330600</v>
       </c>
       <c r="F9" s="3">
-        <v>2145000</v>
+        <v>2167800</v>
       </c>
       <c r="G9" s="3">
-        <v>2052500</v>
+        <v>2102100</v>
       </c>
       <c r="H9" s="3">
-        <v>2199100</v>
+        <v>2011500</v>
       </c>
       <c r="I9" s="3">
-        <v>1947900</v>
+        <v>2155100</v>
       </c>
       <c r="J9" s="3">
+        <v>1909000</v>
+      </c>
+      <c r="K9" s="3">
         <v>1277500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>280200</v>
+        <v>183400</v>
       </c>
       <c r="E10" s="3">
-        <v>936700</v>
+        <v>274600</v>
       </c>
       <c r="F10" s="3">
-        <v>1271600</v>
+        <v>918000</v>
       </c>
       <c r="G10" s="3">
-        <v>977600</v>
+        <v>1246100</v>
       </c>
       <c r="H10" s="3">
-        <v>1693700</v>
+        <v>958100</v>
       </c>
       <c r="I10" s="3">
-        <v>1218500</v>
+        <v>1659800</v>
       </c>
       <c r="J10" s="3">
+        <v>1194100</v>
+      </c>
+      <c r="K10" s="3">
         <v>1001500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -811,20 +824,21 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>4400</v>
+        <v>3800</v>
       </c>
       <c r="E12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F12" s="3">
         <v>4800</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>4</v>
       </c>
@@ -840,8 +854,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,37 +886,43 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>844700</v>
+        <v>49400</v>
       </c>
       <c r="E14" s="3">
+        <v>827800</v>
+      </c>
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
-        <v>-568600</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>-557200</v>
+      </c>
+      <c r="K14" s="3">
         <v>57300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -924,11 +947,14 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -937,66 +963,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3348200</v>
+        <v>2183400</v>
       </c>
       <c r="E17" s="3">
-        <v>2220900</v>
+        <v>3281200</v>
       </c>
       <c r="F17" s="3">
-        <v>2157900</v>
+        <v>2176400</v>
       </c>
       <c r="G17" s="3">
-        <v>2063500</v>
+        <v>2114700</v>
       </c>
       <c r="H17" s="3">
-        <v>2222300</v>
+        <v>2022300</v>
       </c>
       <c r="I17" s="3">
-        <v>1229100</v>
+        <v>2177900</v>
       </c>
       <c r="J17" s="3">
+        <v>1204500</v>
+      </c>
+      <c r="K17" s="3">
         <v>1370300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-689800</v>
+        <v>135000</v>
       </c>
       <c r="E18" s="3">
-        <v>927900</v>
+        <v>-676000</v>
       </c>
       <c r="F18" s="3">
-        <v>1258700</v>
+        <v>909300</v>
       </c>
       <c r="G18" s="3">
-        <v>966600</v>
+        <v>1233500</v>
       </c>
       <c r="H18" s="3">
-        <v>1670500</v>
+        <v>947300</v>
       </c>
       <c r="I18" s="3">
-        <v>1937300</v>
+        <v>1637000</v>
       </c>
       <c r="J18" s="3">
+        <v>1898500</v>
+      </c>
+      <c r="K18" s="3">
         <v>908700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1008,66 +1041,73 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>143700</v>
+        <v>-35100</v>
       </c>
       <c r="E20" s="3">
-        <v>151400</v>
+        <v>140800</v>
       </c>
       <c r="F20" s="3">
-        <v>106100</v>
+        <v>148400</v>
       </c>
       <c r="G20" s="3">
-        <v>133300</v>
+        <v>104000</v>
       </c>
       <c r="H20" s="3">
-        <v>74700</v>
+        <v>130600</v>
       </c>
       <c r="I20" s="3">
-        <v>17800</v>
+        <v>73200</v>
       </c>
       <c r="J20" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K20" s="3">
         <v>85600</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-325200</v>
+        <v>326200</v>
       </c>
       <c r="E21" s="3">
-        <v>1279900</v>
+        <v>-318700</v>
       </c>
       <c r="F21" s="3">
-        <v>1527500</v>
+        <v>1254300</v>
       </c>
       <c r="G21" s="3">
-        <v>1254300</v>
+        <v>1496900</v>
       </c>
       <c r="H21" s="3">
-        <v>1899500</v>
+        <v>1229200</v>
       </c>
       <c r="I21" s="3">
-        <v>2099100</v>
+        <v>1861500</v>
       </c>
       <c r="J21" s="3">
+        <v>2057100</v>
+      </c>
+      <c r="K21" s="3">
         <v>1021900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1092,69 +1132,78 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-546100</v>
+        <v>99900</v>
       </c>
       <c r="E23" s="3">
-        <v>1079300</v>
+        <v>-535200</v>
       </c>
       <c r="F23" s="3">
-        <v>1364700</v>
+        <v>1057700</v>
       </c>
       <c r="G23" s="3">
-        <v>1099900</v>
+        <v>1337400</v>
       </c>
       <c r="H23" s="3">
-        <v>1745200</v>
+        <v>1077900</v>
       </c>
       <c r="I23" s="3">
-        <v>1955100</v>
+        <v>1710200</v>
       </c>
       <c r="J23" s="3">
+        <v>1916000</v>
+      </c>
+      <c r="K23" s="3">
         <v>994300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-74900</v>
+        <v>9300</v>
       </c>
       <c r="E24" s="3">
-        <v>271500</v>
+        <v>-73400</v>
       </c>
       <c r="F24" s="3">
-        <v>342900</v>
+        <v>266100</v>
       </c>
       <c r="G24" s="3">
-        <v>316300</v>
+        <v>336000</v>
       </c>
       <c r="H24" s="3">
-        <v>522700</v>
+        <v>310000</v>
       </c>
       <c r="I24" s="3">
-        <v>570400</v>
+        <v>512300</v>
       </c>
       <c r="J24" s="3">
+        <v>559000</v>
+      </c>
+      <c r="K24" s="3">
         <v>285100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1182,66 +1231,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-471200</v>
+        <v>90600</v>
       </c>
       <c r="E26" s="3">
-        <v>807800</v>
+        <v>-461800</v>
       </c>
       <c r="F26" s="3">
-        <v>1021800</v>
+        <v>791600</v>
       </c>
       <c r="G26" s="3">
-        <v>783600</v>
+        <v>1001400</v>
       </c>
       <c r="H26" s="3">
-        <v>1222400</v>
+        <v>767900</v>
       </c>
       <c r="I26" s="3">
-        <v>1384700</v>
+        <v>1198000</v>
       </c>
       <c r="J26" s="3">
+        <v>1357000</v>
+      </c>
+      <c r="K26" s="3">
         <v>709200</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-494000</v>
+        <v>86200</v>
       </c>
       <c r="E27" s="3">
-        <v>761200</v>
+        <v>-484100</v>
       </c>
       <c r="F27" s="3">
-        <v>992100</v>
+        <v>746000</v>
       </c>
       <c r="G27" s="3">
-        <v>753900</v>
+        <v>972300</v>
       </c>
       <c r="H27" s="3">
-        <v>1196100</v>
+        <v>738800</v>
       </c>
       <c r="I27" s="3">
-        <v>1366200</v>
+        <v>1172100</v>
       </c>
       <c r="J27" s="3">
+        <v>1338900</v>
+      </c>
+      <c r="K27" s="3">
         <v>689300</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1269,8 +1327,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1295,11 +1356,14 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1327,8 +1391,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1356,66 +1423,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-143700</v>
+        <v>35100</v>
       </c>
       <c r="E32" s="3">
-        <v>-151400</v>
+        <v>-140800</v>
       </c>
       <c r="F32" s="3">
-        <v>-106100</v>
+        <v>-148400</v>
       </c>
       <c r="G32" s="3">
-        <v>-133300</v>
+        <v>-104000</v>
       </c>
       <c r="H32" s="3">
-        <v>-74700</v>
+        <v>-130600</v>
       </c>
       <c r="I32" s="3">
-        <v>-17800</v>
+        <v>-73200</v>
       </c>
       <c r="J32" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-85600</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-494000</v>
+        <v>86200</v>
       </c>
       <c r="E33" s="3">
-        <v>761200</v>
+        <v>-484100</v>
       </c>
       <c r="F33" s="3">
-        <v>992100</v>
+        <v>746000</v>
       </c>
       <c r="G33" s="3">
-        <v>753900</v>
+        <v>972300</v>
       </c>
       <c r="H33" s="3">
-        <v>1196100</v>
+        <v>738800</v>
       </c>
       <c r="I33" s="3">
-        <v>1366200</v>
+        <v>1172100</v>
       </c>
       <c r="J33" s="3">
+        <v>1338900</v>
+      </c>
+      <c r="K33" s="3">
         <v>689300</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1443,71 +1519,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-494000</v>
+        <v>86200</v>
       </c>
       <c r="E35" s="3">
-        <v>761200</v>
+        <v>-484100</v>
       </c>
       <c r="F35" s="3">
-        <v>992100</v>
+        <v>746000</v>
       </c>
       <c r="G35" s="3">
-        <v>753900</v>
+        <v>972300</v>
       </c>
       <c r="H35" s="3">
-        <v>1196100</v>
+        <v>738800</v>
       </c>
       <c r="I35" s="3">
-        <v>1366200</v>
+        <v>1172100</v>
       </c>
       <c r="J35" s="3">
+        <v>1338900</v>
+      </c>
+      <c r="K35" s="3">
         <v>689300</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1519,8 +1604,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1532,248 +1618,273 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1461200</v>
+        <v>490500</v>
       </c>
       <c r="E41" s="3">
-        <v>1472200</v>
+        <v>1431900</v>
       </c>
       <c r="F41" s="3">
-        <v>1444000</v>
+        <v>1442800</v>
       </c>
       <c r="G41" s="3">
-        <v>1009900</v>
+        <v>1415100</v>
       </c>
       <c r="H41" s="3">
-        <v>1278900</v>
+        <v>989700</v>
       </c>
       <c r="I41" s="3">
-        <v>1353100</v>
+        <v>1253300</v>
       </c>
       <c r="J41" s="3">
+        <v>1326000</v>
+      </c>
+      <c r="K41" s="3">
         <v>726300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1300</v>
+        <v>2100</v>
       </c>
       <c r="E42" s="3">
-        <v>59300</v>
+        <v>1200</v>
       </c>
       <c r="F42" s="3">
-        <v>57500</v>
+        <v>58100</v>
       </c>
       <c r="G42" s="3">
-        <v>56100</v>
+        <v>56400</v>
       </c>
       <c r="H42" s="3">
-        <v>54800</v>
+        <v>55000</v>
       </c>
       <c r="I42" s="3">
-        <v>200</v>
+        <v>53700</v>
       </c>
       <c r="J42" s="3">
         <v>200</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>200</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>673900</v>
+        <v>596600</v>
       </c>
       <c r="E43" s="3">
-        <v>306200</v>
+        <v>660400</v>
       </c>
       <c r="F43" s="3">
-        <v>367100</v>
+        <v>300100</v>
       </c>
       <c r="G43" s="3">
-        <v>292100</v>
+        <v>359800</v>
       </c>
       <c r="H43" s="3">
-        <v>456100</v>
+        <v>286300</v>
       </c>
       <c r="I43" s="3">
-        <v>252800</v>
+        <v>447000</v>
       </c>
       <c r="J43" s="3">
+        <v>247700</v>
+      </c>
+      <c r="K43" s="3">
         <v>298300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1325000</v>
+        <v>1443100</v>
       </c>
       <c r="E44" s="3">
-        <v>1468800</v>
+        <v>1298400</v>
       </c>
       <c r="F44" s="3">
-        <v>1302000</v>
+        <v>1439400</v>
       </c>
       <c r="G44" s="3">
-        <v>1329600</v>
+        <v>1276000</v>
       </c>
       <c r="H44" s="3">
-        <v>1237300</v>
+        <v>1303000</v>
       </c>
       <c r="I44" s="3">
-        <v>1168300</v>
+        <v>1212500</v>
       </c>
       <c r="J44" s="3">
+        <v>1144900</v>
+      </c>
+      <c r="K44" s="3">
         <v>1059700</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>230500</v>
+        <v>208100</v>
       </c>
       <c r="E45" s="3">
-        <v>188200</v>
+        <v>225800</v>
       </c>
       <c r="F45" s="3">
-        <v>107900</v>
+        <v>184500</v>
       </c>
       <c r="G45" s="3">
-        <v>114200</v>
+        <v>105800</v>
       </c>
       <c r="H45" s="3">
-        <v>60400</v>
+        <v>112000</v>
       </c>
       <c r="I45" s="3">
-        <v>62700</v>
+        <v>59200</v>
       </c>
       <c r="J45" s="3">
+        <v>61500</v>
+      </c>
+      <c r="K45" s="3">
         <v>37000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3691700</v>
+        <v>2740500</v>
       </c>
       <c r="E46" s="3">
-        <v>3494800</v>
+        <v>3617800</v>
       </c>
       <c r="F46" s="3">
-        <v>3278600</v>
+        <v>3424900</v>
       </c>
       <c r="G46" s="3">
-        <v>2802000</v>
+        <v>3213000</v>
       </c>
       <c r="H46" s="3">
-        <v>3087500</v>
+        <v>2745900</v>
       </c>
       <c r="I46" s="3">
-        <v>2837000</v>
+        <v>3025700</v>
       </c>
       <c r="J46" s="3">
+        <v>2780300</v>
+      </c>
+      <c r="K46" s="3">
         <v>2121500</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>923400</v>
+        <v>853000</v>
       </c>
       <c r="E47" s="3">
-        <v>1659900</v>
+        <v>904900</v>
       </c>
       <c r="F47" s="3">
-        <v>1509500</v>
+        <v>1626700</v>
       </c>
       <c r="G47" s="3">
-        <v>1360700</v>
+        <v>1479300</v>
       </c>
       <c r="H47" s="3">
-        <v>449800</v>
+        <v>1333500</v>
       </c>
       <c r="I47" s="3">
-        <v>382300</v>
+        <v>440800</v>
       </c>
       <c r="J47" s="3">
+        <v>374700</v>
+      </c>
+      <c r="K47" s="3">
         <v>323600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3882500</v>
+        <v>3857600</v>
       </c>
       <c r="E48" s="3">
-        <v>3642000</v>
+        <v>3804800</v>
       </c>
       <c r="F48" s="3">
-        <v>3519600</v>
+        <v>3569200</v>
       </c>
       <c r="G48" s="3">
-        <v>3368500</v>
+        <v>3449200</v>
       </c>
       <c r="H48" s="3">
-        <v>3148900</v>
+        <v>3301100</v>
       </c>
       <c r="I48" s="3">
-        <v>3101400</v>
+        <v>3085900</v>
       </c>
       <c r="J48" s="3">
+        <v>3039400</v>
+      </c>
+      <c r="K48" s="3">
         <v>2777100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>537700</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>4</v>
+        <v>527000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>527000</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>4</v>
@@ -1793,8 +1904,11 @@
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1822,8 +1936,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1851,37 +1968,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>192900</v>
+        <v>175900</v>
       </c>
       <c r="E52" s="3">
-        <v>187200</v>
+        <v>189100</v>
       </c>
       <c r="F52" s="3">
-        <v>196000</v>
+        <v>183400</v>
       </c>
       <c r="G52" s="3">
-        <v>201700</v>
+        <v>192000</v>
       </c>
       <c r="H52" s="3">
-        <v>204100</v>
+        <v>197700</v>
       </c>
       <c r="I52" s="3">
-        <v>214100</v>
+        <v>200100</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+        <v>209800</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1909,37 +2032,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9228100</v>
+        <v>8153900</v>
       </c>
       <c r="E54" s="3">
-        <v>8983900</v>
+        <v>9043500</v>
       </c>
       <c r="F54" s="3">
-        <v>8503600</v>
+        <v>8804200</v>
       </c>
       <c r="G54" s="3">
-        <v>7732900</v>
+        <v>8333500</v>
       </c>
       <c r="H54" s="3">
-        <v>6890400</v>
+        <v>7578200</v>
       </c>
       <c r="I54" s="3">
-        <v>6534900</v>
+        <v>6752500</v>
       </c>
       <c r="J54" s="3">
+        <v>6404100</v>
+      </c>
+      <c r="K54" s="3">
         <v>5222200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1951,8 +2080,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1964,182 +2094,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>873900</v>
+        <v>684200</v>
       </c>
       <c r="E57" s="3">
-        <v>858300</v>
+        <v>856400</v>
       </c>
       <c r="F57" s="3">
-        <v>840500</v>
+        <v>841200</v>
       </c>
       <c r="G57" s="3">
-        <v>833800</v>
+        <v>823700</v>
       </c>
       <c r="H57" s="3">
-        <v>882000</v>
+        <v>817100</v>
       </c>
       <c r="I57" s="3">
-        <v>827600</v>
+        <v>864400</v>
       </c>
       <c r="J57" s="3">
+        <v>811000</v>
+      </c>
+      <c r="K57" s="3">
         <v>502300</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>18300</v>
+        <v>76500</v>
       </c>
       <c r="E58" s="3">
-        <v>14800</v>
+        <v>17900</v>
       </c>
       <c r="F58" s="3">
-        <v>13600</v>
+        <v>14500</v>
       </c>
       <c r="G58" s="3">
-        <v>14100</v>
+        <v>13300</v>
       </c>
       <c r="H58" s="3">
-        <v>13100</v>
+        <v>13800</v>
       </c>
       <c r="I58" s="3">
-        <v>81400</v>
+        <v>12900</v>
       </c>
       <c r="J58" s="3">
+        <v>79800</v>
+      </c>
+      <c r="K58" s="3">
         <v>149900</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>70600</v>
+        <v>52500</v>
       </c>
       <c r="E59" s="3">
-        <v>129600</v>
+        <v>69200</v>
       </c>
       <c r="F59" s="3">
-        <v>49500</v>
+        <v>127000</v>
       </c>
       <c r="G59" s="3">
-        <v>97000</v>
+        <v>48500</v>
       </c>
       <c r="H59" s="3">
-        <v>74200</v>
+        <v>95000</v>
       </c>
       <c r="I59" s="3">
-        <v>130600</v>
+        <v>72700</v>
       </c>
       <c r="J59" s="3">
+        <v>128000</v>
+      </c>
+      <c r="K59" s="3">
         <v>28800</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>962800</v>
+        <v>813200</v>
       </c>
       <c r="E60" s="3">
-        <v>1002800</v>
+        <v>943500</v>
       </c>
       <c r="F60" s="3">
-        <v>903700</v>
+        <v>982700</v>
       </c>
       <c r="G60" s="3">
-        <v>944800</v>
+        <v>885600</v>
       </c>
       <c r="H60" s="3">
-        <v>969400</v>
+        <v>925900</v>
       </c>
       <c r="I60" s="3">
-        <v>1039600</v>
+        <v>950000</v>
       </c>
       <c r="J60" s="3">
+        <v>1018800</v>
+      </c>
+      <c r="K60" s="3">
         <v>681000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>122900</v>
+        <v>112700</v>
       </c>
       <c r="E61" s="3">
-        <v>49400</v>
+        <v>120400</v>
       </c>
       <c r="F61" s="3">
-        <v>53000</v>
+        <v>49100</v>
       </c>
       <c r="G61" s="3">
-        <v>59600</v>
+        <v>51900</v>
       </c>
       <c r="H61" s="3">
-        <v>59200</v>
+        <v>58400</v>
       </c>
       <c r="I61" s="3">
-        <v>242900</v>
+        <v>58000</v>
       </c>
       <c r="J61" s="3">
+        <v>238100</v>
+      </c>
+      <c r="K61" s="3">
         <v>339600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1276100</v>
+        <v>1160500</v>
       </c>
       <c r="E62" s="3">
-        <v>1073000</v>
+        <v>1250600</v>
       </c>
       <c r="F62" s="3">
-        <v>1048000</v>
+        <v>1050900</v>
       </c>
       <c r="G62" s="3">
-        <v>1079700</v>
+        <v>1027000</v>
       </c>
       <c r="H62" s="3">
-        <v>921700</v>
+        <v>1058100</v>
       </c>
       <c r="I62" s="3">
-        <v>798600</v>
+        <v>903300</v>
       </c>
       <c r="J62" s="3">
+        <v>782600</v>
+      </c>
+      <c r="K62" s="3">
         <v>685100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2167,8 +2316,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2196,8 +2348,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2225,37 +2380,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2971300</v>
+        <v>2363300</v>
       </c>
       <c r="E66" s="3">
-        <v>2394000</v>
+        <v>2911800</v>
       </c>
       <c r="F66" s="3">
-        <v>2254900</v>
+        <v>2346100</v>
       </c>
       <c r="G66" s="3">
-        <v>2278400</v>
+        <v>2209800</v>
       </c>
       <c r="H66" s="3">
-        <v>2105400</v>
+        <v>2232800</v>
       </c>
       <c r="I66" s="3">
-        <v>2214900</v>
+        <v>2063300</v>
       </c>
       <c r="J66" s="3">
+        <v>2170600</v>
+      </c>
+      <c r="K66" s="3">
         <v>1851100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2267,8 +2428,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2296,8 +2458,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2325,8 +2490,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2351,11 +2519,14 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2383,37 +2554,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4067200</v>
+        <v>3386300</v>
       </c>
       <c r="E72" s="3">
-        <v>4762400</v>
+        <v>3985800</v>
       </c>
       <c r="F72" s="3">
-        <v>4499900</v>
+        <v>4667100</v>
       </c>
       <c r="G72" s="3">
-        <v>3540100</v>
+        <v>4409900</v>
       </c>
       <c r="H72" s="3">
-        <v>3348300</v>
+        <v>3469200</v>
       </c>
       <c r="I72" s="3">
-        <v>2885400</v>
+        <v>3281300</v>
       </c>
       <c r="J72" s="3">
+        <v>2827700</v>
+      </c>
+      <c r="K72" s="3">
         <v>1572000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2441,8 +2618,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2470,8 +2650,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2499,37 +2682,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6256900</v>
+        <v>5790600</v>
       </c>
       <c r="E76" s="3">
-        <v>6590000</v>
+        <v>6131700</v>
       </c>
       <c r="F76" s="3">
-        <v>6248700</v>
+        <v>6458100</v>
       </c>
       <c r="G76" s="3">
-        <v>5454600</v>
+        <v>6123700</v>
       </c>
       <c r="H76" s="3">
-        <v>4784900</v>
+        <v>5345500</v>
       </c>
       <c r="I76" s="3">
-        <v>4319900</v>
+        <v>4689200</v>
       </c>
       <c r="J76" s="3">
+        <v>4233500</v>
+      </c>
+      <c r="K76" s="3">
         <v>3371100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2557,71 +2746,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-494000</v>
+        <v>86200</v>
       </c>
       <c r="E81" s="3">
-        <v>761200</v>
+        <v>-484100</v>
       </c>
       <c r="F81" s="3">
-        <v>992100</v>
+        <v>746000</v>
       </c>
       <c r="G81" s="3">
-        <v>753900</v>
+        <v>972300</v>
       </c>
       <c r="H81" s="3">
-        <v>1196100</v>
+        <v>738800</v>
       </c>
       <c r="I81" s="3">
-        <v>1366200</v>
+        <v>1172100</v>
       </c>
       <c r="J81" s="3">
+        <v>1338900</v>
+      </c>
+      <c r="K81" s="3">
         <v>689300</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2633,37 +2831,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>220900</v>
+        <v>226300</v>
       </c>
       <c r="E83" s="3">
-        <v>200600</v>
+        <v>216400</v>
       </c>
       <c r="F83" s="3">
-        <v>162700</v>
+        <v>196600</v>
       </c>
       <c r="G83" s="3">
-        <v>154400</v>
+        <v>159500</v>
       </c>
       <c r="H83" s="3">
-        <v>154300</v>
+        <v>151300</v>
       </c>
       <c r="I83" s="3">
-        <v>143900</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+        <v>151300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>141100</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2691,8 +2893,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2720,8 +2925,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2749,8 +2957,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2778,8 +2989,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2807,37 +3021,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>494800</v>
+        <v>70000</v>
       </c>
       <c r="E89" s="3">
-        <v>789200</v>
+        <v>484900</v>
       </c>
       <c r="F89" s="3">
-        <v>945000</v>
+        <v>773400</v>
       </c>
       <c r="G89" s="3">
-        <v>958500</v>
+        <v>926100</v>
       </c>
       <c r="H89" s="3">
-        <v>1093300</v>
+        <v>939300</v>
       </c>
       <c r="I89" s="3">
-        <v>1185900</v>
+        <v>1071400</v>
       </c>
       <c r="J89" s="3">
+        <v>1162100</v>
+      </c>
+      <c r="K89" s="3">
         <v>606700</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2849,37 +3069,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6797000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6518000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4838000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5506000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3462000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3717000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2548000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2415000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2907,8 +3131,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2936,37 +3163,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-301000</v>
+        <v>-940700</v>
       </c>
       <c r="E94" s="3">
-        <v>-236500</v>
+        <v>-295000</v>
       </c>
       <c r="F94" s="3">
-        <v>-242500</v>
+        <v>-231800</v>
       </c>
       <c r="G94" s="3">
-        <v>-659800</v>
+        <v>-237600</v>
       </c>
       <c r="H94" s="3">
-        <v>-163500</v>
+        <v>-646600</v>
       </c>
       <c r="I94" s="3">
-        <v>-95400</v>
+        <v>-160200</v>
       </c>
       <c r="J94" s="3">
+        <v>-93500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-76700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2978,37 +3211,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-194500</v>
+        <v>-79400</v>
       </c>
       <c r="E96" s="3">
-        <v>-484700</v>
+        <v>-190600</v>
       </c>
       <c r="F96" s="3">
-        <v>-248700</v>
+        <v>-475000</v>
       </c>
       <c r="G96" s="3">
-        <v>-535500</v>
+        <v>-243700</v>
       </c>
       <c r="H96" s="3">
-        <v>-431900</v>
+        <v>-524800</v>
       </c>
       <c r="I96" s="3">
-        <v>-169600</v>
+        <v>-423300</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-166200</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3036,8 +3273,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3065,8 +3305,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3094,91 +3337,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-238700</v>
+        <v>-91400</v>
       </c>
       <c r="E100" s="3">
-        <v>-541600</v>
+        <v>-234000</v>
       </c>
       <c r="F100" s="3">
-        <v>-274400</v>
+        <v>-530700</v>
       </c>
       <c r="G100" s="3">
-        <v>-592100</v>
+        <v>-268900</v>
       </c>
       <c r="H100" s="3">
-        <v>-988800</v>
+        <v>-580300</v>
       </c>
       <c r="I100" s="3">
-        <v>-431500</v>
+        <v>-969000</v>
       </c>
       <c r="J100" s="3">
+        <v>-422800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-168500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>33800</v>
+        <v>-4300</v>
       </c>
       <c r="E101" s="3">
-        <v>17100</v>
+        <v>33200</v>
       </c>
       <c r="F101" s="3">
-        <v>5900</v>
+        <v>16800</v>
       </c>
       <c r="G101" s="3">
-        <v>24500</v>
+        <v>5800</v>
       </c>
       <c r="H101" s="3">
-        <v>-5700</v>
+        <v>24000</v>
       </c>
       <c r="I101" s="3">
-        <v>-34700</v>
+        <v>-5600</v>
       </c>
       <c r="J101" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="K101" s="3">
         <v>31200</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-11100</v>
+        <v>-966400</v>
       </c>
       <c r="E102" s="3">
-        <v>28200</v>
+        <v>-10800</v>
       </c>
       <c r="F102" s="3">
-        <v>434100</v>
+        <v>27700</v>
       </c>
       <c r="G102" s="3">
-        <v>-269000</v>
+        <v>425400</v>
       </c>
       <c r="H102" s="3">
-        <v>-64800</v>
+        <v>-263600</v>
       </c>
       <c r="I102" s="3">
-        <v>624200</v>
+        <v>-63500</v>
       </c>
       <c r="J102" s="3">
+        <v>611700</v>
+      </c>
+      <c r="K102" s="3">
         <v>392700</v>
       </c>
-      <c r="K102" s="3" t="s">
+      <c r="L102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
@@ -721,25 +721,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2318500</v>
+        <v>2363200</v>
       </c>
       <c r="E8" s="3">
-        <v>2605300</v>
+        <v>2655500</v>
       </c>
       <c r="F8" s="3">
-        <v>3085800</v>
+        <v>3145300</v>
       </c>
       <c r="G8" s="3">
-        <v>3348200</v>
+        <v>3412800</v>
       </c>
       <c r="H8" s="3">
-        <v>2969600</v>
+        <v>3026800</v>
       </c>
       <c r="I8" s="3">
-        <v>3814900</v>
+        <v>3888500</v>
       </c>
       <c r="J8" s="3">
-        <v>3103100</v>
+        <v>3162900</v>
       </c>
       <c r="K8" s="3">
         <v>2279000</v>
@@ -753,25 +753,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2135100</v>
+        <v>2176300</v>
       </c>
       <c r="E9" s="3">
-        <v>2330600</v>
+        <v>2375600</v>
       </c>
       <c r="F9" s="3">
-        <v>2167800</v>
+        <v>2209600</v>
       </c>
       <c r="G9" s="3">
-        <v>2102100</v>
+        <v>2142600</v>
       </c>
       <c r="H9" s="3">
-        <v>2011500</v>
+        <v>2050300</v>
       </c>
       <c r="I9" s="3">
-        <v>2155100</v>
+        <v>2196700</v>
       </c>
       <c r="J9" s="3">
-        <v>1909000</v>
+        <v>1945800</v>
       </c>
       <c r="K9" s="3">
         <v>1277500</v>
@@ -785,25 +785,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>183400</v>
+        <v>186900</v>
       </c>
       <c r="E10" s="3">
-        <v>274600</v>
+        <v>279900</v>
       </c>
       <c r="F10" s="3">
-        <v>918000</v>
+        <v>935700</v>
       </c>
       <c r="G10" s="3">
-        <v>1246100</v>
+        <v>1270200</v>
       </c>
       <c r="H10" s="3">
-        <v>958100</v>
+        <v>976600</v>
       </c>
       <c r="I10" s="3">
-        <v>1659800</v>
+        <v>1691900</v>
       </c>
       <c r="J10" s="3">
-        <v>1194100</v>
+        <v>1217200</v>
       </c>
       <c r="K10" s="3">
         <v>1001500</v>
@@ -831,10 +831,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="E12" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="F12" s="3">
         <v>4800</v>
@@ -895,10 +895,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>49400</v>
+        <v>50300</v>
       </c>
       <c r="E14" s="3">
-        <v>827800</v>
+        <v>843800</v>
       </c>
       <c r="F14" s="3">
         <v>1400</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>-557200</v>
+        <v>-568000</v>
       </c>
       <c r="K14" s="3">
         <v>57300</v>
@@ -970,25 +970,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2183400</v>
+        <v>2225600</v>
       </c>
       <c r="E17" s="3">
-        <v>3281200</v>
+        <v>3344500</v>
       </c>
       <c r="F17" s="3">
-        <v>2176400</v>
+        <v>2218400</v>
       </c>
       <c r="G17" s="3">
-        <v>2114700</v>
+        <v>2155500</v>
       </c>
       <c r="H17" s="3">
-        <v>2022300</v>
+        <v>2061300</v>
       </c>
       <c r="I17" s="3">
-        <v>2177900</v>
+        <v>2219900</v>
       </c>
       <c r="J17" s="3">
-        <v>1204500</v>
+        <v>1227800</v>
       </c>
       <c r="K17" s="3">
         <v>1370300</v>
@@ -1002,25 +1002,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>135000</v>
+        <v>137600</v>
       </c>
       <c r="E18" s="3">
-        <v>-676000</v>
+        <v>-689000</v>
       </c>
       <c r="F18" s="3">
-        <v>909300</v>
+        <v>926900</v>
       </c>
       <c r="G18" s="3">
-        <v>1233500</v>
+        <v>1257300</v>
       </c>
       <c r="H18" s="3">
-        <v>947300</v>
+        <v>965600</v>
       </c>
       <c r="I18" s="3">
-        <v>1637000</v>
+        <v>1668600</v>
       </c>
       <c r="J18" s="3">
-        <v>1898500</v>
+        <v>1935200</v>
       </c>
       <c r="K18" s="3">
         <v>908700</v>
@@ -1048,25 +1048,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-35100</v>
+        <v>-35800</v>
       </c>
       <c r="E20" s="3">
-        <v>140800</v>
+        <v>143500</v>
       </c>
       <c r="F20" s="3">
-        <v>148400</v>
+        <v>151200</v>
       </c>
       <c r="G20" s="3">
-        <v>104000</v>
+        <v>106000</v>
       </c>
       <c r="H20" s="3">
-        <v>130600</v>
+        <v>133100</v>
       </c>
       <c r="I20" s="3">
-        <v>73200</v>
+        <v>74600</v>
       </c>
       <c r="J20" s="3">
-        <v>17500</v>
+        <v>17800</v>
       </c>
       <c r="K20" s="3">
         <v>85600</v>
@@ -1080,25 +1080,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>326200</v>
+        <v>332500</v>
       </c>
       <c r="E21" s="3">
-        <v>-318700</v>
+        <v>-324900</v>
       </c>
       <c r="F21" s="3">
-        <v>1254300</v>
+        <v>1278500</v>
       </c>
       <c r="G21" s="3">
-        <v>1496900</v>
+        <v>1525800</v>
       </c>
       <c r="H21" s="3">
-        <v>1229200</v>
+        <v>1252900</v>
       </c>
       <c r="I21" s="3">
-        <v>1861500</v>
+        <v>1897400</v>
       </c>
       <c r="J21" s="3">
-        <v>2057100</v>
+        <v>2096700</v>
       </c>
       <c r="K21" s="3">
         <v>1021900</v>
@@ -1144,25 +1144,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>99900</v>
+        <v>101900</v>
       </c>
       <c r="E23" s="3">
-        <v>-535200</v>
+        <v>-545500</v>
       </c>
       <c r="F23" s="3">
-        <v>1057700</v>
+        <v>1078100</v>
       </c>
       <c r="G23" s="3">
-        <v>1337400</v>
+        <v>1363200</v>
       </c>
       <c r="H23" s="3">
-        <v>1077900</v>
+        <v>1098700</v>
       </c>
       <c r="I23" s="3">
-        <v>1710200</v>
+        <v>1743200</v>
       </c>
       <c r="J23" s="3">
-        <v>1916000</v>
+        <v>1953000</v>
       </c>
       <c r="K23" s="3">
         <v>994300</v>
@@ -1176,25 +1176,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>9300</v>
+        <v>9500</v>
       </c>
       <c r="E24" s="3">
-        <v>-73400</v>
+        <v>-74800</v>
       </c>
       <c r="F24" s="3">
-        <v>266100</v>
+        <v>271200</v>
       </c>
       <c r="G24" s="3">
-        <v>336000</v>
+        <v>342500</v>
       </c>
       <c r="H24" s="3">
-        <v>310000</v>
+        <v>316000</v>
       </c>
       <c r="I24" s="3">
-        <v>512300</v>
+        <v>522200</v>
       </c>
       <c r="J24" s="3">
-        <v>559000</v>
+        <v>569800</v>
       </c>
       <c r="K24" s="3">
         <v>285100</v>
@@ -1240,25 +1240,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>90600</v>
+        <v>92400</v>
       </c>
       <c r="E26" s="3">
-        <v>-461800</v>
+        <v>-470700</v>
       </c>
       <c r="F26" s="3">
-        <v>791600</v>
+        <v>806900</v>
       </c>
       <c r="G26" s="3">
-        <v>1001400</v>
+        <v>1020700</v>
       </c>
       <c r="H26" s="3">
-        <v>767900</v>
+        <v>782700</v>
       </c>
       <c r="I26" s="3">
-        <v>1198000</v>
+        <v>1221100</v>
       </c>
       <c r="J26" s="3">
-        <v>1357000</v>
+        <v>1383200</v>
       </c>
       <c r="K26" s="3">
         <v>709200</v>
@@ -1272,25 +1272,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>86200</v>
+        <v>87800</v>
       </c>
       <c r="E27" s="3">
-        <v>-484100</v>
+        <v>-493500</v>
       </c>
       <c r="F27" s="3">
-        <v>746000</v>
+        <v>760400</v>
       </c>
       <c r="G27" s="3">
-        <v>972300</v>
+        <v>991000</v>
       </c>
       <c r="H27" s="3">
-        <v>738800</v>
+        <v>753100</v>
       </c>
       <c r="I27" s="3">
-        <v>1172100</v>
+        <v>1194700</v>
       </c>
       <c r="J27" s="3">
-        <v>1338900</v>
+        <v>1364700</v>
       </c>
       <c r="K27" s="3">
         <v>689300</v>
@@ -1432,25 +1432,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>35100</v>
+        <v>35800</v>
       </c>
       <c r="E32" s="3">
-        <v>-140800</v>
+        <v>-143500</v>
       </c>
       <c r="F32" s="3">
-        <v>-148400</v>
+        <v>-151200</v>
       </c>
       <c r="G32" s="3">
-        <v>-104000</v>
+        <v>-106000</v>
       </c>
       <c r="H32" s="3">
-        <v>-130600</v>
+        <v>-133100</v>
       </c>
       <c r="I32" s="3">
-        <v>-73200</v>
+        <v>-74600</v>
       </c>
       <c r="J32" s="3">
-        <v>-17500</v>
+        <v>-17800</v>
       </c>
       <c r="K32" s="3">
         <v>-85600</v>
@@ -1464,25 +1464,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>86200</v>
+        <v>87800</v>
       </c>
       <c r="E33" s="3">
-        <v>-484100</v>
+        <v>-493500</v>
       </c>
       <c r="F33" s="3">
-        <v>746000</v>
+        <v>760400</v>
       </c>
       <c r="G33" s="3">
-        <v>972300</v>
+        <v>991000</v>
       </c>
       <c r="H33" s="3">
-        <v>738800</v>
+        <v>753100</v>
       </c>
       <c r="I33" s="3">
-        <v>1172100</v>
+        <v>1194700</v>
       </c>
       <c r="J33" s="3">
-        <v>1338900</v>
+        <v>1364700</v>
       </c>
       <c r="K33" s="3">
         <v>689300</v>
@@ -1528,25 +1528,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>86200</v>
+        <v>87800</v>
       </c>
       <c r="E35" s="3">
-        <v>-484100</v>
+        <v>-493500</v>
       </c>
       <c r="F35" s="3">
-        <v>746000</v>
+        <v>760400</v>
       </c>
       <c r="G35" s="3">
-        <v>972300</v>
+        <v>991000</v>
       </c>
       <c r="H35" s="3">
-        <v>738800</v>
+        <v>753100</v>
       </c>
       <c r="I35" s="3">
-        <v>1172100</v>
+        <v>1194700</v>
       </c>
       <c r="J35" s="3">
-        <v>1338900</v>
+        <v>1364700</v>
       </c>
       <c r="K35" s="3">
         <v>689300</v>
@@ -1625,25 +1625,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>490500</v>
+        <v>500000</v>
       </c>
       <c r="E41" s="3">
-        <v>1431900</v>
+        <v>1459500</v>
       </c>
       <c r="F41" s="3">
-        <v>1442800</v>
+        <v>1470600</v>
       </c>
       <c r="G41" s="3">
-        <v>1415100</v>
+        <v>1442400</v>
       </c>
       <c r="H41" s="3">
-        <v>989700</v>
+        <v>1008800</v>
       </c>
       <c r="I41" s="3">
-        <v>1253300</v>
+        <v>1277500</v>
       </c>
       <c r="J41" s="3">
-        <v>1326000</v>
+        <v>1351600</v>
       </c>
       <c r="K41" s="3">
         <v>726300</v>
@@ -1660,19 +1660,19 @@
         <v>2100</v>
       </c>
       <c r="E42" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F42" s="3">
-        <v>58100</v>
+        <v>59300</v>
       </c>
       <c r="G42" s="3">
-        <v>56400</v>
+        <v>57500</v>
       </c>
       <c r="H42" s="3">
-        <v>55000</v>
+        <v>56100</v>
       </c>
       <c r="I42" s="3">
-        <v>53700</v>
+        <v>54700</v>
       </c>
       <c r="J42" s="3">
         <v>200</v>
@@ -1689,25 +1689,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>596600</v>
+        <v>608100</v>
       </c>
       <c r="E43" s="3">
-        <v>660400</v>
+        <v>673100</v>
       </c>
       <c r="F43" s="3">
-        <v>300100</v>
+        <v>305800</v>
       </c>
       <c r="G43" s="3">
-        <v>359800</v>
+        <v>366700</v>
       </c>
       <c r="H43" s="3">
-        <v>286300</v>
+        <v>291800</v>
       </c>
       <c r="I43" s="3">
-        <v>447000</v>
+        <v>455600</v>
       </c>
       <c r="J43" s="3">
-        <v>247700</v>
+        <v>252500</v>
       </c>
       <c r="K43" s="3">
         <v>298300</v>
@@ -1721,25 +1721,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1443100</v>
+        <v>1470900</v>
       </c>
       <c r="E44" s="3">
-        <v>1298400</v>
+        <v>1323500</v>
       </c>
       <c r="F44" s="3">
-        <v>1439400</v>
+        <v>1467200</v>
       </c>
       <c r="G44" s="3">
-        <v>1276000</v>
+        <v>1300600</v>
       </c>
       <c r="H44" s="3">
-        <v>1303000</v>
+        <v>1328100</v>
       </c>
       <c r="I44" s="3">
-        <v>1212500</v>
+        <v>1235900</v>
       </c>
       <c r="J44" s="3">
-        <v>1144900</v>
+        <v>1167000</v>
       </c>
       <c r="K44" s="3">
         <v>1059700</v>
@@ -1753,25 +1753,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>208100</v>
+        <v>212100</v>
       </c>
       <c r="E45" s="3">
-        <v>225800</v>
+        <v>230200</v>
       </c>
       <c r="F45" s="3">
-        <v>184500</v>
+        <v>188000</v>
       </c>
       <c r="G45" s="3">
-        <v>105800</v>
+        <v>107800</v>
       </c>
       <c r="H45" s="3">
-        <v>112000</v>
+        <v>114100</v>
       </c>
       <c r="I45" s="3">
-        <v>59200</v>
+        <v>60400</v>
       </c>
       <c r="J45" s="3">
-        <v>61500</v>
+        <v>62600</v>
       </c>
       <c r="K45" s="3">
         <v>37000</v>
@@ -1785,25 +1785,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2740500</v>
+        <v>2793300</v>
       </c>
       <c r="E46" s="3">
-        <v>3617800</v>
+        <v>3687600</v>
       </c>
       <c r="F46" s="3">
-        <v>3424900</v>
+        <v>3490900</v>
       </c>
       <c r="G46" s="3">
-        <v>3213000</v>
+        <v>3275000</v>
       </c>
       <c r="H46" s="3">
-        <v>2745900</v>
+        <v>2798900</v>
       </c>
       <c r="I46" s="3">
-        <v>3025700</v>
+        <v>3084100</v>
       </c>
       <c r="J46" s="3">
-        <v>2780300</v>
+        <v>2833900</v>
       </c>
       <c r="K46" s="3">
         <v>2121500</v>
@@ -1817,25 +1817,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>853000</v>
+        <v>869400</v>
       </c>
       <c r="E47" s="3">
-        <v>904900</v>
+        <v>922400</v>
       </c>
       <c r="F47" s="3">
-        <v>1626700</v>
+        <v>1658100</v>
       </c>
       <c r="G47" s="3">
-        <v>1479300</v>
+        <v>1507800</v>
       </c>
       <c r="H47" s="3">
-        <v>1333500</v>
+        <v>1359200</v>
       </c>
       <c r="I47" s="3">
-        <v>440800</v>
+        <v>449300</v>
       </c>
       <c r="J47" s="3">
-        <v>374700</v>
+        <v>381900</v>
       </c>
       <c r="K47" s="3">
         <v>323600</v>
@@ -1849,25 +1849,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3857600</v>
+        <v>3932100</v>
       </c>
       <c r="E48" s="3">
-        <v>3804800</v>
+        <v>3878200</v>
       </c>
       <c r="F48" s="3">
-        <v>3569200</v>
+        <v>3638000</v>
       </c>
       <c r="G48" s="3">
-        <v>3449200</v>
+        <v>3515700</v>
       </c>
       <c r="H48" s="3">
-        <v>3301100</v>
+        <v>3364800</v>
       </c>
       <c r="I48" s="3">
-        <v>3085900</v>
+        <v>3145400</v>
       </c>
       <c r="J48" s="3">
-        <v>3039400</v>
+        <v>3098000</v>
       </c>
       <c r="K48" s="3">
         <v>2777100</v>
@@ -1881,10 +1881,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>527000</v>
+        <v>537100</v>
       </c>
       <c r="E49" s="3">
-        <v>527000</v>
+        <v>537100</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>4</v>
@@ -1977,25 +1977,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>175900</v>
+        <v>179300</v>
       </c>
       <c r="E52" s="3">
-        <v>189100</v>
+        <v>192700</v>
       </c>
       <c r="F52" s="3">
-        <v>183400</v>
+        <v>187000</v>
       </c>
       <c r="G52" s="3">
-        <v>192000</v>
+        <v>195700</v>
       </c>
       <c r="H52" s="3">
-        <v>197700</v>
+        <v>201500</v>
       </c>
       <c r="I52" s="3">
-        <v>200100</v>
+        <v>203900</v>
       </c>
       <c r="J52" s="3">
-        <v>209800</v>
+        <v>213800</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2041,25 +2041,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>8153900</v>
+        <v>8311200</v>
       </c>
       <c r="E54" s="3">
-        <v>9043500</v>
+        <v>9218000</v>
       </c>
       <c r="F54" s="3">
-        <v>8804200</v>
+        <v>8974000</v>
       </c>
       <c r="G54" s="3">
-        <v>8333500</v>
+        <v>8494300</v>
       </c>
       <c r="H54" s="3">
-        <v>7578200</v>
+        <v>7724400</v>
       </c>
       <c r="I54" s="3">
-        <v>6752500</v>
+        <v>6882800</v>
       </c>
       <c r="J54" s="3">
-        <v>6404100</v>
+        <v>6527700</v>
       </c>
       <c r="K54" s="3">
         <v>5222200</v>
@@ -2101,25 +2101,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>684200</v>
+        <v>697400</v>
       </c>
       <c r="E57" s="3">
-        <v>856400</v>
+        <v>873000</v>
       </c>
       <c r="F57" s="3">
-        <v>841200</v>
+        <v>857400</v>
       </c>
       <c r="G57" s="3">
-        <v>823700</v>
+        <v>839600</v>
       </c>
       <c r="H57" s="3">
-        <v>817100</v>
+        <v>832800</v>
       </c>
       <c r="I57" s="3">
-        <v>864400</v>
+        <v>881100</v>
       </c>
       <c r="J57" s="3">
-        <v>811000</v>
+        <v>826700</v>
       </c>
       <c r="K57" s="3">
         <v>502300</v>
@@ -2133,25 +2133,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>76500</v>
+        <v>77900</v>
       </c>
       <c r="E58" s="3">
-        <v>17900</v>
+        <v>18200</v>
       </c>
       <c r="F58" s="3">
-        <v>14500</v>
+        <v>14800</v>
       </c>
       <c r="G58" s="3">
-        <v>13300</v>
+        <v>13600</v>
       </c>
       <c r="H58" s="3">
-        <v>13800</v>
+        <v>14100</v>
       </c>
       <c r="I58" s="3">
-        <v>12900</v>
+        <v>13100</v>
       </c>
       <c r="J58" s="3">
-        <v>79800</v>
+        <v>81300</v>
       </c>
       <c r="K58" s="3">
         <v>149900</v>
@@ -2165,25 +2165,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>52500</v>
+        <v>53500</v>
       </c>
       <c r="E59" s="3">
-        <v>69200</v>
+        <v>70500</v>
       </c>
       <c r="F59" s="3">
-        <v>127000</v>
+        <v>129500</v>
       </c>
       <c r="G59" s="3">
-        <v>48500</v>
+        <v>49500</v>
       </c>
       <c r="H59" s="3">
-        <v>95000</v>
+        <v>96900</v>
       </c>
       <c r="I59" s="3">
-        <v>72700</v>
+        <v>74100</v>
       </c>
       <c r="J59" s="3">
-        <v>128000</v>
+        <v>130500</v>
       </c>
       <c r="K59" s="3">
         <v>28800</v>
@@ -2197,25 +2197,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>813200</v>
+        <v>828900</v>
       </c>
       <c r="E60" s="3">
-        <v>943500</v>
+        <v>961700</v>
       </c>
       <c r="F60" s="3">
-        <v>982700</v>
+        <v>1001700</v>
       </c>
       <c r="G60" s="3">
-        <v>885600</v>
+        <v>902700</v>
       </c>
       <c r="H60" s="3">
-        <v>925900</v>
+        <v>943800</v>
       </c>
       <c r="I60" s="3">
-        <v>950000</v>
+        <v>968300</v>
       </c>
       <c r="J60" s="3">
-        <v>1018800</v>
+        <v>1038500</v>
       </c>
       <c r="K60" s="3">
         <v>681000</v>
@@ -2229,25 +2229,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>112700</v>
+        <v>114900</v>
       </c>
       <c r="E61" s="3">
-        <v>120400</v>
+        <v>122700</v>
       </c>
       <c r="F61" s="3">
-        <v>49100</v>
+        <v>50000</v>
       </c>
       <c r="G61" s="3">
-        <v>51900</v>
+        <v>53000</v>
       </c>
       <c r="H61" s="3">
-        <v>58400</v>
+        <v>59500</v>
       </c>
       <c r="I61" s="3">
-        <v>58000</v>
+        <v>59200</v>
       </c>
       <c r="J61" s="3">
-        <v>238100</v>
+        <v>242700</v>
       </c>
       <c r="K61" s="3">
         <v>339600</v>
@@ -2261,25 +2261,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1160500</v>
+        <v>1182900</v>
       </c>
       <c r="E62" s="3">
-        <v>1250600</v>
+        <v>1274700</v>
       </c>
       <c r="F62" s="3">
-        <v>1050900</v>
+        <v>1071100</v>
       </c>
       <c r="G62" s="3">
-        <v>1027000</v>
+        <v>1046800</v>
       </c>
       <c r="H62" s="3">
-        <v>1058100</v>
+        <v>1078500</v>
       </c>
       <c r="I62" s="3">
-        <v>903300</v>
+        <v>920700</v>
       </c>
       <c r="J62" s="3">
-        <v>782600</v>
+        <v>797700</v>
       </c>
       <c r="K62" s="3">
         <v>685100</v>
@@ -2389,25 +2389,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2363300</v>
+        <v>2408900</v>
       </c>
       <c r="E66" s="3">
-        <v>2911800</v>
+        <v>2968000</v>
       </c>
       <c r="F66" s="3">
-        <v>2346100</v>
+        <v>2391300</v>
       </c>
       <c r="G66" s="3">
-        <v>2209800</v>
+        <v>2252400</v>
       </c>
       <c r="H66" s="3">
-        <v>2232800</v>
+        <v>2275800</v>
       </c>
       <c r="I66" s="3">
-        <v>2063300</v>
+        <v>2103100</v>
       </c>
       <c r="J66" s="3">
-        <v>2170600</v>
+        <v>2212500</v>
       </c>
       <c r="K66" s="3">
         <v>1851100</v>
@@ -2563,25 +2563,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3386300</v>
+        <v>3451600</v>
       </c>
       <c r="E72" s="3">
-        <v>3985800</v>
+        <v>4062700</v>
       </c>
       <c r="F72" s="3">
-        <v>4667100</v>
+        <v>4757200</v>
       </c>
       <c r="G72" s="3">
-        <v>4409900</v>
+        <v>4495000</v>
       </c>
       <c r="H72" s="3">
-        <v>3469200</v>
+        <v>3536200</v>
       </c>
       <c r="I72" s="3">
-        <v>3281300</v>
+        <v>3344700</v>
       </c>
       <c r="J72" s="3">
-        <v>2827700</v>
+        <v>2882200</v>
       </c>
       <c r="K72" s="3">
         <v>1572000</v>
@@ -2691,25 +2691,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5790600</v>
+        <v>5902300</v>
       </c>
       <c r="E76" s="3">
-        <v>6131700</v>
+        <v>6250000</v>
       </c>
       <c r="F76" s="3">
-        <v>6458100</v>
+        <v>6582700</v>
       </c>
       <c r="G76" s="3">
-        <v>6123700</v>
+        <v>6241800</v>
       </c>
       <c r="H76" s="3">
-        <v>5345500</v>
+        <v>5448600</v>
       </c>
       <c r="I76" s="3">
-        <v>4689200</v>
+        <v>4779700</v>
       </c>
       <c r="J76" s="3">
-        <v>4233500</v>
+        <v>4315200</v>
       </c>
       <c r="K76" s="3">
         <v>3371100</v>
@@ -2792,25 +2792,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>86200</v>
+        <v>87800</v>
       </c>
       <c r="E81" s="3">
-        <v>-484100</v>
+        <v>-493500</v>
       </c>
       <c r="F81" s="3">
-        <v>746000</v>
+        <v>760400</v>
       </c>
       <c r="G81" s="3">
-        <v>972300</v>
+        <v>991000</v>
       </c>
       <c r="H81" s="3">
-        <v>738800</v>
+        <v>753100</v>
       </c>
       <c r="I81" s="3">
-        <v>1172100</v>
+        <v>1194700</v>
       </c>
       <c r="J81" s="3">
-        <v>1338900</v>
+        <v>1364700</v>
       </c>
       <c r="K81" s="3">
         <v>689300</v>
@@ -2838,25 +2838,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>226300</v>
+        <v>230600</v>
       </c>
       <c r="E83" s="3">
-        <v>216400</v>
+        <v>220600</v>
       </c>
       <c r="F83" s="3">
-        <v>196600</v>
+        <v>200400</v>
       </c>
       <c r="G83" s="3">
-        <v>159500</v>
+        <v>162600</v>
       </c>
       <c r="H83" s="3">
-        <v>151300</v>
+        <v>154200</v>
       </c>
       <c r="I83" s="3">
-        <v>151300</v>
+        <v>154200</v>
       </c>
       <c r="J83" s="3">
-        <v>141100</v>
+        <v>143800</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
@@ -3030,25 +3030,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>70000</v>
+        <v>71400</v>
       </c>
       <c r="E89" s="3">
-        <v>484900</v>
+        <v>494300</v>
       </c>
       <c r="F89" s="3">
-        <v>773400</v>
+        <v>788300</v>
       </c>
       <c r="G89" s="3">
-        <v>926100</v>
+        <v>944000</v>
       </c>
       <c r="H89" s="3">
-        <v>939300</v>
+        <v>957400</v>
       </c>
       <c r="I89" s="3">
-        <v>1071400</v>
+        <v>1092000</v>
       </c>
       <c r="J89" s="3">
-        <v>1162100</v>
+        <v>1184600</v>
       </c>
       <c r="K89" s="3">
         <v>606700</v>
@@ -3172,25 +3172,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-940700</v>
+        <v>-958900</v>
       </c>
       <c r="E94" s="3">
-        <v>-295000</v>
+        <v>-300700</v>
       </c>
       <c r="F94" s="3">
-        <v>-231800</v>
+        <v>-236200</v>
       </c>
       <c r="G94" s="3">
-        <v>-237600</v>
+        <v>-242200</v>
       </c>
       <c r="H94" s="3">
-        <v>-646600</v>
+        <v>-659100</v>
       </c>
       <c r="I94" s="3">
-        <v>-160200</v>
+        <v>-163300</v>
       </c>
       <c r="J94" s="3">
-        <v>-93500</v>
+        <v>-95300</v>
       </c>
       <c r="K94" s="3">
         <v>-76700</v>
@@ -3218,25 +3218,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-79400</v>
+        <v>-80900</v>
       </c>
       <c r="E96" s="3">
-        <v>-190600</v>
+        <v>-194300</v>
       </c>
       <c r="F96" s="3">
-        <v>-475000</v>
+        <v>-484100</v>
       </c>
       <c r="G96" s="3">
-        <v>-243700</v>
+        <v>-248400</v>
       </c>
       <c r="H96" s="3">
-        <v>-524800</v>
+        <v>-534900</v>
       </c>
       <c r="I96" s="3">
-        <v>-423300</v>
+        <v>-431400</v>
       </c>
       <c r="J96" s="3">
-        <v>-166200</v>
+        <v>-169400</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3346,25 +3346,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-91400</v>
+        <v>-93200</v>
       </c>
       <c r="E100" s="3">
-        <v>-234000</v>
+        <v>-238500</v>
       </c>
       <c r="F100" s="3">
-        <v>-530700</v>
+        <v>-541000</v>
       </c>
       <c r="G100" s="3">
-        <v>-268900</v>
+        <v>-274100</v>
       </c>
       <c r="H100" s="3">
-        <v>-580300</v>
+        <v>-591500</v>
       </c>
       <c r="I100" s="3">
-        <v>-969000</v>
+        <v>-987700</v>
       </c>
       <c r="J100" s="3">
-        <v>-422800</v>
+        <v>-431000</v>
       </c>
       <c r="K100" s="3">
         <v>-168500</v>
@@ -3378,25 +3378,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="E101" s="3">
-        <v>33200</v>
+        <v>33800</v>
       </c>
       <c r="F101" s="3">
-        <v>16800</v>
+        <v>17100</v>
       </c>
       <c r="G101" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="H101" s="3">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="I101" s="3">
-        <v>-5600</v>
+        <v>-5700</v>
       </c>
       <c r="J101" s="3">
-        <v>-34000</v>
+        <v>-34700</v>
       </c>
       <c r="K101" s="3">
         <v>31200</v>
@@ -3410,25 +3410,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-966400</v>
+        <v>-985100</v>
       </c>
       <c r="E102" s="3">
-        <v>-10800</v>
+        <v>-11000</v>
       </c>
       <c r="F102" s="3">
-        <v>27700</v>
+        <v>28200</v>
       </c>
       <c r="G102" s="3">
-        <v>425400</v>
+        <v>433600</v>
       </c>
       <c r="H102" s="3">
-        <v>-263600</v>
+        <v>-268700</v>
       </c>
       <c r="I102" s="3">
-        <v>-63500</v>
+        <v>-64700</v>
       </c>
       <c r="J102" s="3">
-        <v>611700</v>
+        <v>623500</v>
       </c>
       <c r="K102" s="3">
         <v>392700</v>

--- a/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
@@ -656,163 +656,176 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2363200</v>
+        <v>2421500</v>
       </c>
       <c r="E8" s="3">
-        <v>2655500</v>
+        <v>2447000</v>
       </c>
       <c r="F8" s="3">
-        <v>3145300</v>
+        <v>2749700</v>
       </c>
       <c r="G8" s="3">
-        <v>3412800</v>
+        <v>3256900</v>
       </c>
       <c r="H8" s="3">
-        <v>3026800</v>
+        <v>3533800</v>
       </c>
       <c r="I8" s="3">
-        <v>3888500</v>
+        <v>3134200</v>
       </c>
       <c r="J8" s="3">
+        <v>4026400</v>
+      </c>
+      <c r="K8" s="3">
         <v>3162900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2279000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2176300</v>
+        <v>2307000</v>
       </c>
       <c r="E9" s="3">
-        <v>2375600</v>
+        <v>2253400</v>
       </c>
       <c r="F9" s="3">
-        <v>2209600</v>
+        <v>2459800</v>
       </c>
       <c r="G9" s="3">
-        <v>2142600</v>
+        <v>2288000</v>
       </c>
       <c r="H9" s="3">
-        <v>2050300</v>
+        <v>2218600</v>
       </c>
       <c r="I9" s="3">
-        <v>2196700</v>
+        <v>2123000</v>
       </c>
       <c r="J9" s="3">
+        <v>2274600</v>
+      </c>
+      <c r="K9" s="3">
         <v>1945800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1277500</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>186900</v>
+        <v>114500</v>
       </c>
       <c r="E10" s="3">
-        <v>279900</v>
+        <v>193600</v>
       </c>
       <c r="F10" s="3">
-        <v>935700</v>
+        <v>289900</v>
       </c>
       <c r="G10" s="3">
-        <v>1270200</v>
+        <v>968900</v>
       </c>
       <c r="H10" s="3">
-        <v>976600</v>
+        <v>1315200</v>
       </c>
       <c r="I10" s="3">
-        <v>1691900</v>
+        <v>1011200</v>
       </c>
       <c r="J10" s="3">
+        <v>1751900</v>
+      </c>
+      <c r="K10" s="3">
         <v>1217200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1001500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -825,22 +838,23 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>3900</v>
+        <v>900</v>
       </c>
       <c r="E12" s="3">
-        <v>4400</v>
+        <v>4100</v>
       </c>
       <c r="F12" s="3">
-        <v>4800</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
+        <v>4500</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5000</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>4</v>
@@ -857,8 +871,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,40 +906,46 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>50300</v>
+        <v>1211900</v>
       </c>
       <c r="E14" s="3">
-        <v>843800</v>
+        <v>52100</v>
       </c>
       <c r="F14" s="3">
-        <v>1400</v>
+        <v>873700</v>
       </c>
       <c r="G14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H14" s="3">
         <v>-700</v>
       </c>
-      <c r="H14" s="3">
-        <v>4200</v>
-      </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-568000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>57300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -950,11 +973,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -964,72 +990,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2225600</v>
+        <v>3602900</v>
       </c>
       <c r="E17" s="3">
-        <v>3344500</v>
+        <v>2304500</v>
       </c>
       <c r="F17" s="3">
-        <v>2218400</v>
+        <v>3463200</v>
       </c>
       <c r="G17" s="3">
-        <v>2155500</v>
+        <v>2297100</v>
       </c>
       <c r="H17" s="3">
-        <v>2061300</v>
+        <v>2232000</v>
       </c>
       <c r="I17" s="3">
-        <v>2219900</v>
+        <v>2134400</v>
       </c>
       <c r="J17" s="3">
+        <v>2298600</v>
+      </c>
+      <c r="K17" s="3">
         <v>1227800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1370300</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>137600</v>
+        <v>-1181400</v>
       </c>
       <c r="E18" s="3">
-        <v>-689000</v>
+        <v>142500</v>
       </c>
       <c r="F18" s="3">
-        <v>926900</v>
+        <v>-713400</v>
       </c>
       <c r="G18" s="3">
-        <v>1257300</v>
+        <v>959800</v>
       </c>
       <c r="H18" s="3">
-        <v>965600</v>
+        <v>1301900</v>
       </c>
       <c r="I18" s="3">
-        <v>1668600</v>
+        <v>999800</v>
       </c>
       <c r="J18" s="3">
+        <v>1727800</v>
+      </c>
+      <c r="K18" s="3">
         <v>1935200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>908700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1042,72 +1075,79 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-35800</v>
+        <v>-75100</v>
       </c>
       <c r="E20" s="3">
-        <v>143500</v>
+        <v>-37000</v>
       </c>
       <c r="F20" s="3">
-        <v>151200</v>
+        <v>148600</v>
       </c>
       <c r="G20" s="3">
-        <v>106000</v>
+        <v>156600</v>
       </c>
       <c r="H20" s="3">
-        <v>133100</v>
+        <v>109700</v>
       </c>
       <c r="I20" s="3">
-        <v>74600</v>
+        <v>137800</v>
       </c>
       <c r="J20" s="3">
+        <v>77300</v>
+      </c>
+      <c r="K20" s="3">
         <v>17800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>85600</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>332500</v>
+        <v>-1042000</v>
       </c>
       <c r="E21" s="3">
-        <v>-324900</v>
+        <v>344300</v>
       </c>
       <c r="F21" s="3">
-        <v>1278500</v>
+        <v>-336400</v>
       </c>
       <c r="G21" s="3">
-        <v>1525800</v>
+        <v>1323800</v>
       </c>
       <c r="H21" s="3">
-        <v>1252900</v>
+        <v>1579900</v>
       </c>
       <c r="I21" s="3">
-        <v>1897400</v>
+        <v>1297300</v>
       </c>
       <c r="J21" s="3">
+        <v>1964700</v>
+      </c>
+      <c r="K21" s="3">
         <v>2096700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1021900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1135,75 +1175,84 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>101900</v>
+        <v>-1256500</v>
       </c>
       <c r="E23" s="3">
-        <v>-545500</v>
+        <v>105500</v>
       </c>
       <c r="F23" s="3">
-        <v>1078100</v>
+        <v>-564900</v>
       </c>
       <c r="G23" s="3">
-        <v>1363200</v>
+        <v>1116300</v>
       </c>
       <c r="H23" s="3">
-        <v>1098700</v>
+        <v>1411600</v>
       </c>
       <c r="I23" s="3">
-        <v>1743200</v>
+        <v>1137700</v>
       </c>
       <c r="J23" s="3">
+        <v>1805100</v>
+      </c>
+      <c r="K23" s="3">
         <v>1953000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>994300</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>9500</v>
+        <v>-194400</v>
       </c>
       <c r="E24" s="3">
-        <v>-74800</v>
+        <v>9900</v>
       </c>
       <c r="F24" s="3">
-        <v>271200</v>
+        <v>-77500</v>
       </c>
       <c r="G24" s="3">
-        <v>342500</v>
+        <v>280800</v>
       </c>
       <c r="H24" s="3">
-        <v>316000</v>
+        <v>354700</v>
       </c>
       <c r="I24" s="3">
-        <v>522200</v>
+        <v>327200</v>
       </c>
       <c r="J24" s="3">
+        <v>540700</v>
+      </c>
+      <c r="K24" s="3">
         <v>569800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>285100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1234,72 +1283,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>92400</v>
+        <v>-1062100</v>
       </c>
       <c r="E26" s="3">
-        <v>-470700</v>
+        <v>95600</v>
       </c>
       <c r="F26" s="3">
-        <v>806900</v>
+        <v>-487400</v>
       </c>
       <c r="G26" s="3">
-        <v>1020700</v>
+        <v>835500</v>
       </c>
       <c r="H26" s="3">
-        <v>782700</v>
+        <v>1056900</v>
       </c>
       <c r="I26" s="3">
-        <v>1221100</v>
+        <v>810500</v>
       </c>
       <c r="J26" s="3">
+        <v>1264400</v>
+      </c>
+      <c r="K26" s="3">
         <v>1383200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>709200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>87800</v>
+        <v>-1066500</v>
       </c>
       <c r="E27" s="3">
-        <v>-493500</v>
+        <v>90900</v>
       </c>
       <c r="F27" s="3">
-        <v>760400</v>
+        <v>-511000</v>
       </c>
       <c r="G27" s="3">
-        <v>991000</v>
+        <v>787400</v>
       </c>
       <c r="H27" s="3">
-        <v>753100</v>
+        <v>1026200</v>
       </c>
       <c r="I27" s="3">
-        <v>1194700</v>
+        <v>779800</v>
       </c>
       <c r="J27" s="3">
+        <v>1237100</v>
+      </c>
+      <c r="K27" s="3">
         <v>1364700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>689300</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1330,8 +1388,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1359,11 +1420,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1394,8 +1458,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1426,72 +1493,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>35800</v>
+        <v>75100</v>
       </c>
       <c r="E32" s="3">
-        <v>-143500</v>
+        <v>37000</v>
       </c>
       <c r="F32" s="3">
-        <v>-151200</v>
+        <v>-148600</v>
       </c>
       <c r="G32" s="3">
-        <v>-106000</v>
+        <v>-156600</v>
       </c>
       <c r="H32" s="3">
-        <v>-133100</v>
+        <v>-109700</v>
       </c>
       <c r="I32" s="3">
-        <v>-74600</v>
+        <v>-137800</v>
       </c>
       <c r="J32" s="3">
+        <v>-77300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-17800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-85600</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>87800</v>
+        <v>-1066500</v>
       </c>
       <c r="E33" s="3">
-        <v>-493500</v>
+        <v>90900</v>
       </c>
       <c r="F33" s="3">
-        <v>760400</v>
+        <v>-511000</v>
       </c>
       <c r="G33" s="3">
-        <v>991000</v>
+        <v>787400</v>
       </c>
       <c r="H33" s="3">
-        <v>753100</v>
+        <v>1026200</v>
       </c>
       <c r="I33" s="3">
-        <v>1194700</v>
+        <v>779800</v>
       </c>
       <c r="J33" s="3">
+        <v>1237100</v>
+      </c>
+      <c r="K33" s="3">
         <v>1364700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>689300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1522,77 +1598,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>87800</v>
+        <v>-1066500</v>
       </c>
       <c r="E35" s="3">
-        <v>-493500</v>
+        <v>90900</v>
       </c>
       <c r="F35" s="3">
-        <v>760400</v>
+        <v>-511000</v>
       </c>
       <c r="G35" s="3">
-        <v>991000</v>
+        <v>787400</v>
       </c>
       <c r="H35" s="3">
-        <v>753100</v>
+        <v>1026200</v>
       </c>
       <c r="I35" s="3">
-        <v>1194700</v>
+        <v>779800</v>
       </c>
       <c r="J35" s="3">
+        <v>1237100</v>
+      </c>
+      <c r="K35" s="3">
         <v>1364700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>689300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1605,8 +1690,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1619,275 +1705,300 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>500000</v>
+        <v>542600</v>
       </c>
       <c r="E41" s="3">
-        <v>1459500</v>
+        <v>517700</v>
       </c>
       <c r="F41" s="3">
-        <v>1470600</v>
+        <v>1511300</v>
       </c>
       <c r="G41" s="3">
-        <v>1442400</v>
+        <v>1522700</v>
       </c>
       <c r="H41" s="3">
-        <v>1008800</v>
+        <v>1493600</v>
       </c>
       <c r="I41" s="3">
-        <v>1277500</v>
+        <v>1044600</v>
       </c>
       <c r="J41" s="3">
+        <v>1322800</v>
+      </c>
+      <c r="K41" s="3">
         <v>1351600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>726300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="E42" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F42" s="3">
         <v>1300</v>
       </c>
-      <c r="F42" s="3">
-        <v>59300</v>
-      </c>
       <c r="G42" s="3">
-        <v>57500</v>
+        <v>61400</v>
       </c>
       <c r="H42" s="3">
-        <v>56100</v>
+        <v>59500</v>
       </c>
       <c r="I42" s="3">
-        <v>54700</v>
+        <v>58000</v>
       </c>
       <c r="J42" s="3">
-        <v>200</v>
+        <v>56700</v>
       </c>
       <c r="K42" s="3">
         <v>200</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>200</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>608100</v>
+        <v>711000</v>
       </c>
       <c r="E43" s="3">
-        <v>673100</v>
+        <v>629700</v>
       </c>
       <c r="F43" s="3">
-        <v>305800</v>
+        <v>697000</v>
       </c>
       <c r="G43" s="3">
-        <v>366700</v>
+        <v>316700</v>
       </c>
       <c r="H43" s="3">
-        <v>291800</v>
+        <v>379700</v>
       </c>
       <c r="I43" s="3">
-        <v>455600</v>
+        <v>302100</v>
       </c>
       <c r="J43" s="3">
+        <v>471800</v>
+      </c>
+      <c r="K43" s="3">
         <v>252500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>298300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1470900</v>
+        <v>1497700</v>
       </c>
       <c r="E44" s="3">
-        <v>1323500</v>
+        <v>1523100</v>
       </c>
       <c r="F44" s="3">
-        <v>1467200</v>
+        <v>1370400</v>
       </c>
       <c r="G44" s="3">
-        <v>1300600</v>
+        <v>1519300</v>
       </c>
       <c r="H44" s="3">
-        <v>1328100</v>
+        <v>1346700</v>
       </c>
       <c r="I44" s="3">
-        <v>1235900</v>
+        <v>1375200</v>
       </c>
       <c r="J44" s="3">
+        <v>1279800</v>
+      </c>
+      <c r="K44" s="3">
         <v>1167000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1059700</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>212100</v>
+        <v>97400</v>
       </c>
       <c r="E45" s="3">
-        <v>230200</v>
+        <v>219700</v>
       </c>
       <c r="F45" s="3">
-        <v>188000</v>
+        <v>238400</v>
       </c>
       <c r="G45" s="3">
-        <v>107800</v>
+        <v>194700</v>
       </c>
       <c r="H45" s="3">
-        <v>114100</v>
+        <v>111600</v>
       </c>
       <c r="I45" s="3">
-        <v>60400</v>
+        <v>118200</v>
       </c>
       <c r="J45" s="3">
+        <v>62500</v>
+      </c>
+      <c r="K45" s="3">
         <v>62600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>37000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2793300</v>
+        <v>2850600</v>
       </c>
       <c r="E46" s="3">
-        <v>3687600</v>
+        <v>2892400</v>
       </c>
       <c r="F46" s="3">
-        <v>3490900</v>
+        <v>3818400</v>
       </c>
       <c r="G46" s="3">
-        <v>3275000</v>
+        <v>3614700</v>
       </c>
       <c r="H46" s="3">
-        <v>2798900</v>
+        <v>3391100</v>
       </c>
       <c r="I46" s="3">
-        <v>3084100</v>
+        <v>2898100</v>
       </c>
       <c r="J46" s="3">
+        <v>3193500</v>
+      </c>
+      <c r="K46" s="3">
         <v>2833900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2121500</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>869400</v>
+        <v>848000</v>
       </c>
       <c r="E47" s="3">
-        <v>922400</v>
+        <v>900200</v>
       </c>
       <c r="F47" s="3">
-        <v>1658100</v>
+        <v>955100</v>
       </c>
       <c r="G47" s="3">
-        <v>1507800</v>
+        <v>1716900</v>
       </c>
       <c r="H47" s="3">
-        <v>1359200</v>
+        <v>1561300</v>
       </c>
       <c r="I47" s="3">
-        <v>449300</v>
+        <v>1407500</v>
       </c>
       <c r="J47" s="3">
+        <v>465300</v>
+      </c>
+      <c r="K47" s="3">
         <v>381900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>323600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3932100</v>
+        <v>3583200</v>
       </c>
       <c r="E48" s="3">
-        <v>3878200</v>
+        <v>4071500</v>
       </c>
       <c r="F48" s="3">
-        <v>3638000</v>
+        <v>4015700</v>
       </c>
       <c r="G48" s="3">
-        <v>3515700</v>
+        <v>3767100</v>
       </c>
       <c r="H48" s="3">
-        <v>3364800</v>
+        <v>3640400</v>
       </c>
       <c r="I48" s="3">
-        <v>3145400</v>
+        <v>3484100</v>
       </c>
       <c r="J48" s="3">
+        <v>3257000</v>
+      </c>
+      <c r="K48" s="3">
         <v>3098000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2777100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>537100</v>
+        <v>198500</v>
       </c>
       <c r="E49" s="3">
-        <v>537100</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
+        <v>556200</v>
+      </c>
+      <c r="F49" s="3">
+        <v>556200</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>4</v>
@@ -1907,8 +2018,11 @@
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1939,8 +2053,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1971,40 +2088,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>179300</v>
+        <v>11700</v>
       </c>
       <c r="E52" s="3">
-        <v>192700</v>
+        <v>185700</v>
       </c>
       <c r="F52" s="3">
-        <v>187000</v>
+        <v>199500</v>
       </c>
       <c r="G52" s="3">
-        <v>195700</v>
+        <v>193600</v>
       </c>
       <c r="H52" s="3">
-        <v>201500</v>
+        <v>202700</v>
       </c>
       <c r="I52" s="3">
-        <v>203900</v>
+        <v>208700</v>
       </c>
       <c r="J52" s="3">
+        <v>211100</v>
+      </c>
+      <c r="K52" s="3">
         <v>213800</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2035,40 +2158,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>8311200</v>
+        <v>7492000</v>
       </c>
       <c r="E54" s="3">
-        <v>9218000</v>
+        <v>8606000</v>
       </c>
       <c r="F54" s="3">
-        <v>8974000</v>
+        <v>9544900</v>
       </c>
       <c r="G54" s="3">
-        <v>8494300</v>
+        <v>9292300</v>
       </c>
       <c r="H54" s="3">
-        <v>7724400</v>
+        <v>8795500</v>
       </c>
       <c r="I54" s="3">
-        <v>6882800</v>
+        <v>7998400</v>
       </c>
       <c r="J54" s="3">
+        <v>7126900</v>
+      </c>
+      <c r="K54" s="3">
         <v>6527700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5222200</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2081,8 +2210,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2095,200 +2225,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>697400</v>
+        <v>833900</v>
       </c>
       <c r="E57" s="3">
-        <v>873000</v>
+        <v>722200</v>
       </c>
       <c r="F57" s="3">
-        <v>857400</v>
+        <v>903900</v>
       </c>
       <c r="G57" s="3">
-        <v>839600</v>
+        <v>887800</v>
       </c>
       <c r="H57" s="3">
-        <v>832800</v>
+        <v>869400</v>
       </c>
       <c r="I57" s="3">
-        <v>881100</v>
+        <v>862400</v>
       </c>
       <c r="J57" s="3">
+        <v>912300</v>
+      </c>
+      <c r="K57" s="3">
         <v>826700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>502300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>77900</v>
+        <v>80500</v>
       </c>
       <c r="E58" s="3">
-        <v>18200</v>
+        <v>80700</v>
       </c>
       <c r="F58" s="3">
-        <v>14800</v>
+        <v>18900</v>
       </c>
       <c r="G58" s="3">
-        <v>13600</v>
+        <v>15300</v>
       </c>
       <c r="H58" s="3">
         <v>14100</v>
       </c>
       <c r="I58" s="3">
-        <v>13100</v>
+        <v>14600</v>
       </c>
       <c r="J58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="K58" s="3">
         <v>81300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>149900</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>53500</v>
+        <v>34800</v>
       </c>
       <c r="E59" s="3">
-        <v>70500</v>
+        <v>55400</v>
       </c>
       <c r="F59" s="3">
-        <v>129500</v>
+        <v>73000</v>
       </c>
       <c r="G59" s="3">
-        <v>49500</v>
+        <v>134100</v>
       </c>
       <c r="H59" s="3">
-        <v>96900</v>
+        <v>51200</v>
       </c>
       <c r="I59" s="3">
-        <v>74100</v>
+        <v>100300</v>
       </c>
       <c r="J59" s="3">
+        <v>76700</v>
+      </c>
+      <c r="K59" s="3">
         <v>130500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>28800</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>828900</v>
+        <v>949200</v>
       </c>
       <c r="E60" s="3">
-        <v>961700</v>
+        <v>858300</v>
       </c>
       <c r="F60" s="3">
-        <v>1001700</v>
+        <v>995800</v>
       </c>
       <c r="G60" s="3">
-        <v>902700</v>
+        <v>1037200</v>
       </c>
       <c r="H60" s="3">
-        <v>943800</v>
+        <v>934700</v>
       </c>
       <c r="I60" s="3">
-        <v>968300</v>
+        <v>977300</v>
       </c>
       <c r="J60" s="3">
+        <v>1002600</v>
+      </c>
+      <c r="K60" s="3">
         <v>1038500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>681000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>114900</v>
+        <v>107700</v>
       </c>
       <c r="E61" s="3">
-        <v>122700</v>
+        <v>118700</v>
       </c>
       <c r="F61" s="3">
-        <v>50000</v>
+        <v>127100</v>
       </c>
       <c r="G61" s="3">
-        <v>53000</v>
+        <v>51100</v>
       </c>
       <c r="H61" s="3">
-        <v>59500</v>
+        <v>54800</v>
       </c>
       <c r="I61" s="3">
-        <v>59200</v>
+        <v>61600</v>
       </c>
       <c r="J61" s="3">
+        <v>61300</v>
+      </c>
+      <c r="K61" s="3">
         <v>242700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>339600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1182900</v>
+        <v>990300</v>
       </c>
       <c r="E62" s="3">
-        <v>1274700</v>
+        <v>1225000</v>
       </c>
       <c r="F62" s="3">
-        <v>1071100</v>
+        <v>1319900</v>
       </c>
       <c r="G62" s="3">
-        <v>1046800</v>
+        <v>1109800</v>
       </c>
       <c r="H62" s="3">
-        <v>1078500</v>
+        <v>1083900</v>
       </c>
       <c r="I62" s="3">
-        <v>920700</v>
+        <v>1116700</v>
       </c>
       <c r="J62" s="3">
+        <v>953400</v>
+      </c>
+      <c r="K62" s="3">
         <v>797700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>685100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2319,8 +2468,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2351,8 +2503,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2383,40 +2538,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2408900</v>
+        <v>2341700</v>
       </c>
       <c r="E66" s="3">
-        <v>2968000</v>
+        <v>2494300</v>
       </c>
       <c r="F66" s="3">
-        <v>2391300</v>
+        <v>3073300</v>
       </c>
       <c r="G66" s="3">
-        <v>2252400</v>
+        <v>2476100</v>
       </c>
       <c r="H66" s="3">
-        <v>2275800</v>
+        <v>2332300</v>
       </c>
       <c r="I66" s="3">
-        <v>2103100</v>
+        <v>2356600</v>
       </c>
       <c r="J66" s="3">
+        <v>2177700</v>
+      </c>
+      <c r="K66" s="3">
         <v>2212500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1851100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2429,8 +2590,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2461,8 +2623,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2493,8 +2658,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2522,11 +2690,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2557,40 +2728,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3451600</v>
+        <v>2620100</v>
       </c>
       <c r="E72" s="3">
-        <v>4062700</v>
+        <v>3574100</v>
       </c>
       <c r="F72" s="3">
-        <v>4757200</v>
+        <v>4206800</v>
       </c>
       <c r="G72" s="3">
-        <v>4495000</v>
+        <v>4925900</v>
       </c>
       <c r="H72" s="3">
-        <v>3536200</v>
+        <v>4654400</v>
       </c>
       <c r="I72" s="3">
-        <v>3344700</v>
+        <v>3661600</v>
       </c>
       <c r="J72" s="3">
+        <v>3463300</v>
+      </c>
+      <c r="K72" s="3">
         <v>2882200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1572000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2621,8 +2798,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2653,8 +2833,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2685,40 +2868,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5902300</v>
+        <v>5150300</v>
       </c>
       <c r="E76" s="3">
-        <v>6250000</v>
+        <v>6111700</v>
       </c>
       <c r="F76" s="3">
-        <v>6582700</v>
+        <v>6471600</v>
       </c>
       <c r="G76" s="3">
-        <v>6241800</v>
+        <v>6816200</v>
       </c>
       <c r="H76" s="3">
-        <v>5448600</v>
+        <v>6463200</v>
       </c>
       <c r="I76" s="3">
-        <v>4779700</v>
+        <v>5641800</v>
       </c>
       <c r="J76" s="3">
+        <v>4949200</v>
+      </c>
+      <c r="K76" s="3">
         <v>4315200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3371100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2749,77 +2938,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>87800</v>
+        <v>-1066500</v>
       </c>
       <c r="E81" s="3">
-        <v>-493500</v>
+        <v>90900</v>
       </c>
       <c r="F81" s="3">
-        <v>760400</v>
+        <v>-511000</v>
       </c>
       <c r="G81" s="3">
-        <v>991000</v>
+        <v>787400</v>
       </c>
       <c r="H81" s="3">
-        <v>753100</v>
+        <v>1026200</v>
       </c>
       <c r="I81" s="3">
-        <v>1194700</v>
+        <v>779800</v>
       </c>
       <c r="J81" s="3">
+        <v>1237100</v>
+      </c>
+      <c r="K81" s="3">
         <v>1364700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>689300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2832,40 +3030,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>230600</v>
+        <v>214500</v>
       </c>
       <c r="E83" s="3">
-        <v>220600</v>
+        <v>238800</v>
       </c>
       <c r="F83" s="3">
-        <v>200400</v>
+        <v>228400</v>
       </c>
       <c r="G83" s="3">
-        <v>162600</v>
+        <v>207500</v>
       </c>
       <c r="H83" s="3">
-        <v>154200</v>
+        <v>168300</v>
       </c>
       <c r="I83" s="3">
-        <v>154200</v>
+        <v>159700</v>
       </c>
       <c r="J83" s="3">
+        <v>159600</v>
+      </c>
+      <c r="K83" s="3">
         <v>143800</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2896,8 +3098,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2928,8 +3133,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2960,8 +3168,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2992,8 +3203,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3024,40 +3238,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>71400</v>
+        <v>317200</v>
       </c>
       <c r="E89" s="3">
-        <v>494300</v>
+        <v>73900</v>
       </c>
       <c r="F89" s="3">
-        <v>788300</v>
+        <v>511800</v>
       </c>
       <c r="G89" s="3">
-        <v>944000</v>
+        <v>816300</v>
       </c>
       <c r="H89" s="3">
-        <v>957400</v>
+        <v>977400</v>
       </c>
       <c r="I89" s="3">
-        <v>1092000</v>
+        <v>991400</v>
       </c>
       <c r="J89" s="3">
+        <v>1130800</v>
+      </c>
+      <c r="K89" s="3">
         <v>1184600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>606700</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3070,40 +3290,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7183000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6797000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6518000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4838000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5506000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3462000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3717000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2548000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2415000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3134,8 +3358,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3166,40 +3393,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-958900</v>
+        <v>370200</v>
       </c>
       <c r="E94" s="3">
-        <v>-300700</v>
+        <v>-992900</v>
       </c>
       <c r="F94" s="3">
-        <v>-236200</v>
+        <v>-295800</v>
       </c>
       <c r="G94" s="3">
-        <v>-242200</v>
+        <v>-244600</v>
       </c>
       <c r="H94" s="3">
-        <v>-659100</v>
+        <v>-250800</v>
       </c>
       <c r="I94" s="3">
-        <v>-163300</v>
+        <v>-682500</v>
       </c>
       <c r="J94" s="3">
+        <v>-169100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-95300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-76700</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3212,40 +3445,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-80900</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-194300</v>
+        <v>-83800</v>
       </c>
       <c r="F96" s="3">
-        <v>-484100</v>
+        <v>-201200</v>
       </c>
       <c r="G96" s="3">
-        <v>-248400</v>
+        <v>-501300</v>
       </c>
       <c r="H96" s="3">
-        <v>-534900</v>
+        <v>-257200</v>
       </c>
       <c r="I96" s="3">
-        <v>-431400</v>
+        <v>-553900</v>
       </c>
       <c r="J96" s="3">
+        <v>-446700</v>
+      </c>
+      <c r="K96" s="3">
         <v>-169400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3276,8 +3513,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3308,8 +3548,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3340,100 +3583,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-93200</v>
+        <v>-630400</v>
       </c>
       <c r="E100" s="3">
-        <v>-238500</v>
+        <v>-96500</v>
       </c>
       <c r="F100" s="3">
-        <v>-541000</v>
+        <v>-246900</v>
       </c>
       <c r="G100" s="3">
-        <v>-274100</v>
+        <v>-560200</v>
       </c>
       <c r="H100" s="3">
-        <v>-591500</v>
+        <v>-283800</v>
       </c>
       <c r="I100" s="3">
-        <v>-987700</v>
+        <v>-612500</v>
       </c>
       <c r="J100" s="3">
+        <v>-1022800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-431000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-168500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-4400</v>
+        <v>-5700</v>
       </c>
       <c r="E101" s="3">
-        <v>33800</v>
+        <v>-4600</v>
       </c>
       <c r="F101" s="3">
-        <v>17100</v>
+        <v>35000</v>
       </c>
       <c r="G101" s="3">
-        <v>5900</v>
+        <v>17700</v>
       </c>
       <c r="H101" s="3">
-        <v>24500</v>
+        <v>6100</v>
       </c>
       <c r="I101" s="3">
-        <v>-5700</v>
+        <v>25400</v>
       </c>
       <c r="J101" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="K101" s="3">
         <v>-34700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>31200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-985100</v>
+        <v>51300</v>
       </c>
       <c r="E102" s="3">
-        <v>-11000</v>
+        <v>-1020000</v>
       </c>
       <c r="F102" s="3">
-        <v>28200</v>
+        <v>-11400</v>
       </c>
       <c r="G102" s="3">
-        <v>433600</v>
+        <v>29200</v>
       </c>
       <c r="H102" s="3">
-        <v>-268700</v>
+        <v>449000</v>
       </c>
       <c r="I102" s="3">
-        <v>-64700</v>
+        <v>-278200</v>
       </c>
       <c r="J102" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="K102" s="3">
         <v>623500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>392700</v>
       </c>
-      <c r="L102" s="3" t="s">
+      <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>IMPUY</t>
   </si>
@@ -663,13 +663,11 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="1"/>
@@ -693,22 +691,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44377</v>
       </c>
       <c r="K7" s="2">
         <v>44196</v>
@@ -724,26 +722,26 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>2421500</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2447000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2749700</v>
-      </c>
-      <c r="G8" s="3">
-        <v>3256900</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3533800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3134200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>4026400</v>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>3162900</v>
@@ -759,26 +757,26 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>2307000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2253400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2459800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2288000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2218600</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2123000</v>
-      </c>
-      <c r="J9" s="3">
-        <v>2274600</v>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K9" s="3">
         <v>1945800</v>
@@ -794,26 +792,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>114500</v>
-      </c>
-      <c r="E10" s="3">
-        <v>193600</v>
-      </c>
-      <c r="F10" s="3">
-        <v>289900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>968900</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1315200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1011200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1751900</v>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K10" s="3">
         <v>1217200</v>
@@ -844,17 +842,17 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>900</v>
-      </c>
-      <c r="E12" s="3">
-        <v>4100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>4500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>5000</v>
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>4</v>
@@ -914,26 +912,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>1211900</v>
-      </c>
-      <c r="E14" s="3">
-        <v>52100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>873700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I14" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>-568000</v>
@@ -949,26 +947,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -996,26 +994,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>3602900</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2304500</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3463200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2297100</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2232000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2134400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2298600</v>
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K17" s="3">
         <v>1227800</v>
@@ -1031,26 +1029,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-1181400</v>
-      </c>
-      <c r="E18" s="3">
-        <v>142500</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-713400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>959800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1301900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>999800</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1727800</v>
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K18" s="3">
         <v>1935200</v>
@@ -1081,26 +1079,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-75100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-37000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>148600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>156600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>109700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>137800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>77300</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>17800</v>
@@ -1116,26 +1114,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>-1042000</v>
-      </c>
-      <c r="E21" s="3">
-        <v>344300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-336400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1323800</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1579900</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1297300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1964700</v>
+      <c r="D21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K21" s="3">
         <v>2096700</v>
@@ -1151,26 +1149,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1186,26 +1184,26 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-1256500</v>
-      </c>
-      <c r="E23" s="3">
-        <v>105500</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-564900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1116300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1411600</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1137700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1805100</v>
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K23" s="3">
         <v>1953000</v>
@@ -1221,26 +1219,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>-194400</v>
-      </c>
-      <c r="E24" s="3">
-        <v>9900</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-77500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>280800</v>
-      </c>
-      <c r="H24" s="3">
-        <v>354700</v>
-      </c>
-      <c r="I24" s="3">
-        <v>327200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>540700</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>569800</v>
@@ -1291,26 +1289,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-1062100</v>
-      </c>
-      <c r="E26" s="3">
-        <v>95600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-487400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>835500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1056900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>810500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1264400</v>
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K26" s="3">
         <v>1383200</v>
@@ -1326,26 +1324,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-1066500</v>
-      </c>
-      <c r="E27" s="3">
-        <v>90900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-511000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>787400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1026200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>779800</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1237100</v>
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K27" s="3">
         <v>1364700</v>
@@ -1396,26 +1394,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1501,26 +1499,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>75100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>37000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-148600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-156600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-109700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-137800</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-77300</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>-17800</v>
@@ -1536,26 +1534,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-1066500</v>
-      </c>
-      <c r="E33" s="3">
-        <v>90900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-511000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>787400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1026200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>779800</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1237100</v>
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K33" s="3">
         <v>1364700</v>
@@ -1606,26 +1604,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-1066500</v>
-      </c>
-      <c r="E35" s="3">
-        <v>90900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-511000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>787400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1026200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>779800</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1237100</v>
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K35" s="3">
         <v>1364700</v>
@@ -1650,22 +1648,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44377</v>
       </c>
       <c r="K38" s="2">
         <v>44196</v>
@@ -1712,25 +1710,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>542600</v>
+        <v>527500</v>
       </c>
       <c r="E41" s="3">
-        <v>517700</v>
+        <v>509700</v>
       </c>
       <c r="F41" s="3">
-        <v>1511300</v>
+        <v>502300</v>
       </c>
       <c r="G41" s="3">
-        <v>1522700</v>
+        <v>487000</v>
       </c>
       <c r="H41" s="3">
-        <v>1493600</v>
+        <v>1423900</v>
       </c>
       <c r="I41" s="3">
-        <v>1044600</v>
+        <v>1513900</v>
       </c>
       <c r="J41" s="3">
-        <v>1322800</v>
+        <v>1589500</v>
       </c>
       <c r="K41" s="3">
         <v>1351600</v>
@@ -1750,22 +1748,22 @@
         <v>1900</v>
       </c>
       <c r="E42" s="3">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="F42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I42" s="3">
         <v>1300</v>
       </c>
-      <c r="G42" s="3">
-        <v>61400</v>
-      </c>
-      <c r="H42" s="3">
-        <v>59500</v>
-      </c>
-      <c r="I42" s="3">
-        <v>58000</v>
-      </c>
       <c r="J42" s="3">
-        <v>56700</v>
+        <v>64100</v>
       </c>
       <c r="K42" s="3">
         <v>200</v>
@@ -1782,25 +1780,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>711000</v>
+        <v>691100</v>
       </c>
       <c r="E43" s="3">
-        <v>629700</v>
+        <v>667900</v>
       </c>
       <c r="F43" s="3">
-        <v>697000</v>
+        <v>610900</v>
       </c>
       <c r="G43" s="3">
-        <v>316700</v>
+        <v>592300</v>
       </c>
       <c r="H43" s="3">
-        <v>379700</v>
+        <v>656700</v>
       </c>
       <c r="I43" s="3">
-        <v>302100</v>
+        <v>698200</v>
       </c>
       <c r="J43" s="3">
-        <v>471800</v>
+        <v>330600</v>
       </c>
       <c r="K43" s="3">
         <v>252500</v>
@@ -1817,25 +1815,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1497700</v>
+        <v>1455900</v>
       </c>
       <c r="E44" s="3">
-        <v>1523100</v>
+        <v>1406800</v>
       </c>
       <c r="F44" s="3">
-        <v>1370400</v>
+        <v>1477700</v>
       </c>
       <c r="G44" s="3">
-        <v>1519300</v>
+        <v>1432600</v>
       </c>
       <c r="H44" s="3">
-        <v>1346700</v>
+        <v>1291200</v>
       </c>
       <c r="I44" s="3">
-        <v>1375200</v>
+        <v>1372800</v>
       </c>
       <c r="J44" s="3">
-        <v>1279800</v>
+        <v>1585800</v>
       </c>
       <c r="K44" s="3">
         <v>1167000</v>
@@ -1851,26 +1849,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>97400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>219700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>238400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>194700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>111600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>118200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>62500</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>62600</v>
@@ -1887,25 +1885,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2850600</v>
+        <v>2771100</v>
       </c>
       <c r="E46" s="3">
-        <v>2892400</v>
+        <v>2677700</v>
       </c>
       <c r="F46" s="3">
-        <v>3818400</v>
+        <v>2806200</v>
       </c>
       <c r="G46" s="3">
-        <v>3614700</v>
+        <v>2720600</v>
       </c>
       <c r="H46" s="3">
-        <v>3391100</v>
+        <v>3597600</v>
       </c>
       <c r="I46" s="3">
-        <v>2898100</v>
+        <v>3825100</v>
       </c>
       <c r="J46" s="3">
-        <v>3193500</v>
+        <v>3773100</v>
       </c>
       <c r="K46" s="3">
         <v>2833900</v>
@@ -1922,25 +1920,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>848000</v>
+        <v>824400</v>
       </c>
       <c r="E47" s="3">
-        <v>900200</v>
+        <v>796600</v>
       </c>
       <c r="F47" s="3">
-        <v>955100</v>
+        <v>873400</v>
       </c>
       <c r="G47" s="3">
-        <v>1716900</v>
+        <v>846800</v>
       </c>
       <c r="H47" s="3">
-        <v>1561300</v>
+        <v>899800</v>
       </c>
       <c r="I47" s="3">
-        <v>1407500</v>
+        <v>956700</v>
       </c>
       <c r="J47" s="3">
-        <v>465300</v>
+        <v>1792100</v>
       </c>
       <c r="K47" s="3">
         <v>381900</v>
@@ -1957,25 +1955,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3583200</v>
+        <v>3478600</v>
       </c>
       <c r="E48" s="3">
-        <v>4071500</v>
+        <v>3361300</v>
       </c>
       <c r="F48" s="3">
-        <v>4015700</v>
+        <v>3945300</v>
       </c>
       <c r="G48" s="3">
-        <v>3767100</v>
+        <v>3825000</v>
       </c>
       <c r="H48" s="3">
-        <v>3640400</v>
+        <v>3778800</v>
       </c>
       <c r="I48" s="3">
-        <v>3484100</v>
+        <v>4017800</v>
       </c>
       <c r="J48" s="3">
-        <v>3257000</v>
+        <v>3927000</v>
       </c>
       <c r="K48" s="3">
         <v>3098000</v>
@@ -1992,25 +1990,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>198500</v>
+        <v>193000</v>
       </c>
       <c r="E49" s="3">
-        <v>556200</v>
+        <v>186500</v>
       </c>
       <c r="F49" s="3">
-        <v>556200</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+        <v>539600</v>
+      </c>
+      <c r="G49" s="3">
+        <v>523100</v>
+      </c>
+      <c r="H49" s="3">
+        <v>524000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>557100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
@@ -2097,25 +2095,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11700</v>
+        <v>16100</v>
       </c>
       <c r="E52" s="3">
-        <v>185700</v>
+        <v>15600</v>
       </c>
       <c r="F52" s="3">
-        <v>199500</v>
+        <v>184900</v>
       </c>
       <c r="G52" s="3">
-        <v>193600</v>
+        <v>179300</v>
       </c>
       <c r="H52" s="3">
-        <v>202700</v>
+        <v>192700</v>
       </c>
       <c r="I52" s="3">
-        <v>208700</v>
+        <v>204900</v>
       </c>
       <c r="J52" s="3">
-        <v>211100</v>
+        <v>207300</v>
       </c>
       <c r="K52" s="3">
         <v>213800</v>
@@ -2167,25 +2165,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>7492000</v>
+        <v>7283200</v>
       </c>
       <c r="E54" s="3">
-        <v>8606000</v>
+        <v>7037700</v>
       </c>
       <c r="F54" s="3">
-        <v>9544900</v>
+        <v>8349500</v>
       </c>
       <c r="G54" s="3">
-        <v>9292300</v>
+        <v>8094800</v>
       </c>
       <c r="H54" s="3">
-        <v>8795500</v>
+        <v>8992900</v>
       </c>
       <c r="I54" s="3">
-        <v>7998400</v>
+        <v>9561600</v>
       </c>
       <c r="J54" s="3">
-        <v>7126900</v>
+        <v>9699500</v>
       </c>
       <c r="K54" s="3">
         <v>6527700</v>
@@ -2232,25 +2230,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>833900</v>
+        <v>683800</v>
       </c>
       <c r="E57" s="3">
-        <v>722200</v>
+        <v>660800</v>
       </c>
       <c r="F57" s="3">
-        <v>903900</v>
+        <v>700700</v>
       </c>
       <c r="G57" s="3">
-        <v>887800</v>
+        <v>679300</v>
       </c>
       <c r="H57" s="3">
-        <v>869400</v>
+        <v>718400</v>
       </c>
       <c r="I57" s="3">
-        <v>862400</v>
+        <v>763900</v>
       </c>
       <c r="J57" s="3">
-        <v>912300</v>
+        <v>926700</v>
       </c>
       <c r="K57" s="3">
         <v>826700</v>
@@ -2267,25 +2265,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>80500</v>
+        <v>78300</v>
       </c>
       <c r="E58" s="3">
-        <v>80700</v>
+        <v>75600</v>
       </c>
       <c r="F58" s="3">
+        <v>78300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>75900</v>
+      </c>
+      <c r="H58" s="3">
+        <v>17800</v>
+      </c>
+      <c r="I58" s="3">
         <v>18900</v>
       </c>
-      <c r="G58" s="3">
-        <v>15300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>14100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>14600</v>
-      </c>
       <c r="J58" s="3">
-        <v>13600</v>
+        <v>16000</v>
       </c>
       <c r="K58" s="3">
         <v>81300</v>
@@ -2302,25 +2300,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>34800</v>
+        <v>39900</v>
       </c>
       <c r="E59" s="3">
-        <v>55400</v>
+        <v>38500</v>
       </c>
       <c r="F59" s="3">
-        <v>73000</v>
+        <v>53700</v>
       </c>
       <c r="G59" s="3">
-        <v>134100</v>
+        <v>52100</v>
       </c>
       <c r="H59" s="3">
-        <v>51200</v>
+        <v>77100</v>
       </c>
       <c r="I59" s="3">
-        <v>100300</v>
+        <v>82000</v>
       </c>
       <c r="J59" s="3">
-        <v>76700</v>
+        <v>139900</v>
       </c>
       <c r="K59" s="3">
         <v>130500</v>
@@ -2337,25 +2335,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>949200</v>
+        <v>922700</v>
       </c>
       <c r="E60" s="3">
-        <v>858300</v>
+        <v>891600</v>
       </c>
       <c r="F60" s="3">
-        <v>995800</v>
+        <v>832700</v>
       </c>
       <c r="G60" s="3">
-        <v>1037200</v>
+        <v>807300</v>
       </c>
       <c r="H60" s="3">
-        <v>934700</v>
+        <v>938200</v>
       </c>
       <c r="I60" s="3">
-        <v>977300</v>
+        <v>997600</v>
       </c>
       <c r="J60" s="3">
-        <v>1002600</v>
+        <v>1082600</v>
       </c>
       <c r="K60" s="3">
         <v>1038500</v>
@@ -2372,25 +2370,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>107700</v>
+        <v>104700</v>
       </c>
       <c r="E61" s="3">
-        <v>118700</v>
+        <v>101200</v>
       </c>
       <c r="F61" s="3">
-        <v>127100</v>
+        <v>115200</v>
       </c>
       <c r="G61" s="3">
-        <v>51100</v>
+        <v>111700</v>
       </c>
       <c r="H61" s="3">
-        <v>54800</v>
+        <v>119700</v>
       </c>
       <c r="I61" s="3">
-        <v>61600</v>
+        <v>127300</v>
       </c>
       <c r="J61" s="3">
-        <v>61300</v>
+        <v>53300</v>
       </c>
       <c r="K61" s="3">
         <v>242700</v>
@@ -2407,25 +2405,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>990300</v>
+        <v>159700</v>
       </c>
       <c r="E62" s="3">
-        <v>1225000</v>
+        <v>154400</v>
       </c>
       <c r="F62" s="3">
-        <v>1319900</v>
+        <v>161000</v>
       </c>
       <c r="G62" s="3">
-        <v>1109800</v>
+        <v>156100</v>
       </c>
       <c r="H62" s="3">
-        <v>1083900</v>
+        <v>158300</v>
       </c>
       <c r="I62" s="3">
-        <v>1116700</v>
+        <v>168300</v>
       </c>
       <c r="J62" s="3">
-        <v>953400</v>
+        <v>148500</v>
       </c>
       <c r="K62" s="3">
         <v>797700</v>
@@ -2547,25 +2545,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2341700</v>
+        <v>1990100</v>
       </c>
       <c r="E66" s="3">
-        <v>2494300</v>
+        <v>1923000</v>
       </c>
       <c r="F66" s="3">
-        <v>3073300</v>
+        <v>2136400</v>
       </c>
       <c r="G66" s="3">
-        <v>2476100</v>
+        <v>2071200</v>
       </c>
       <c r="H66" s="3">
-        <v>2332300</v>
+        <v>2301600</v>
       </c>
       <c r="I66" s="3">
-        <v>2356600</v>
+        <v>2447100</v>
       </c>
       <c r="J66" s="3">
-        <v>2177700</v>
+        <v>2294400</v>
       </c>
       <c r="K66" s="3">
         <v>2212500</v>
@@ -2737,25 +2735,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2620100</v>
+        <v>2425400</v>
       </c>
       <c r="E72" s="3">
-        <v>3574100</v>
+        <v>2343600</v>
       </c>
       <c r="F72" s="3">
-        <v>4206800</v>
+        <v>3457100</v>
       </c>
       <c r="G72" s="3">
-        <v>4925900</v>
+        <v>3351600</v>
       </c>
       <c r="H72" s="3">
-        <v>4654400</v>
+        <v>3938000</v>
       </c>
       <c r="I72" s="3">
-        <v>3661600</v>
+        <v>4187100</v>
       </c>
       <c r="J72" s="3">
-        <v>3463300</v>
+        <v>5124200</v>
       </c>
       <c r="K72" s="3">
         <v>2882200</v>
@@ -2877,25 +2875,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5150300</v>
+        <v>5006800</v>
       </c>
       <c r="E76" s="3">
-        <v>6111700</v>
+        <v>4838000</v>
       </c>
       <c r="F76" s="3">
-        <v>6471600</v>
+        <v>5929500</v>
       </c>
       <c r="G76" s="3">
-        <v>6816200</v>
+        <v>5748600</v>
       </c>
       <c r="H76" s="3">
-        <v>6463200</v>
+        <v>6097400</v>
       </c>
       <c r="I76" s="3">
-        <v>5641800</v>
+        <v>6482900</v>
       </c>
       <c r="J76" s="3">
-        <v>4949200</v>
+        <v>7114900</v>
       </c>
       <c r="K76" s="3">
         <v>4315200</v>
@@ -2955,22 +2953,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44377</v>
       </c>
       <c r="K80" s="2">
         <v>44196</v>
@@ -2986,26 +2984,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-1066500</v>
-      </c>
-      <c r="E81" s="3">
-        <v>90900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-511000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>787400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1026200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>779800</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1237100</v>
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K81" s="3">
         <v>1364700</v>
@@ -3037,25 +3035,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>214500</v>
+        <v>107600</v>
       </c>
       <c r="E83" s="3">
-        <v>238800</v>
+        <v>114400</v>
       </c>
       <c r="F83" s="3">
-        <v>228400</v>
+        <v>108300</v>
       </c>
       <c r="G83" s="3">
-        <v>207500</v>
+        <v>102200</v>
       </c>
       <c r="H83" s="3">
-        <v>168300</v>
+        <v>91200</v>
       </c>
       <c r="I83" s="3">
-        <v>159700</v>
+        <v>102100</v>
       </c>
       <c r="J83" s="3">
-        <v>159600</v>
+        <v>88800</v>
       </c>
       <c r="K83" s="3">
         <v>143800</v>
@@ -3247,25 +3245,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>317200</v>
+        <v>154200</v>
       </c>
       <c r="E89" s="3">
-        <v>73900</v>
+        <v>149000</v>
       </c>
       <c r="F89" s="3">
-        <v>511800</v>
+        <v>35900</v>
       </c>
       <c r="G89" s="3">
-        <v>816300</v>
+        <v>34800</v>
       </c>
       <c r="H89" s="3">
-        <v>977400</v>
+        <v>241100</v>
       </c>
       <c r="I89" s="3">
-        <v>991400</v>
+        <v>256400</v>
       </c>
       <c r="J89" s="3">
-        <v>1130800</v>
+        <v>426000</v>
       </c>
       <c r="K89" s="3">
         <v>1184600</v>
@@ -3297,25 +3295,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-7183000</v>
+        <v>-196700</v>
       </c>
       <c r="E91" s="3">
-        <v>-6797000</v>
+        <v>-190100</v>
       </c>
       <c r="F91" s="3">
-        <v>-6518000</v>
+        <v>-185800</v>
       </c>
       <c r="G91" s="3">
-        <v>-4838000</v>
+        <v>-180100</v>
       </c>
       <c r="H91" s="3">
-        <v>-5506000</v>
+        <v>-207900</v>
       </c>
       <c r="I91" s="3">
-        <v>-3462000</v>
+        <v>-221100</v>
       </c>
       <c r="J91" s="3">
-        <v>-3717000</v>
+        <v>-142300</v>
       </c>
       <c r="K91" s="3">
         <v>-2548000</v>
@@ -3402,25 +3400,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>370200</v>
+        <v>179900</v>
       </c>
       <c r="E94" s="3">
-        <v>-992900</v>
+        <v>173900</v>
       </c>
       <c r="F94" s="3">
-        <v>-295800</v>
+        <v>-481600</v>
       </c>
       <c r="G94" s="3">
-        <v>-244600</v>
+        <v>-467000</v>
       </c>
       <c r="H94" s="3">
-        <v>-250800</v>
+        <v>-139400</v>
       </c>
       <c r="I94" s="3">
-        <v>-682500</v>
+        <v>-148200</v>
       </c>
       <c r="J94" s="3">
-        <v>-169100</v>
+        <v>-127700</v>
       </c>
       <c r="K94" s="3">
         <v>-95300</v>
@@ -3455,22 +3453,22 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-83800</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-201200</v>
+        <v>40600</v>
       </c>
       <c r="G96" s="3">
-        <v>-501300</v>
+        <v>39400</v>
       </c>
       <c r="H96" s="3">
-        <v>-257200</v>
+        <v>94800</v>
       </c>
       <c r="I96" s="3">
-        <v>-553900</v>
+        <v>100800</v>
       </c>
       <c r="J96" s="3">
-        <v>-446700</v>
+        <v>261600</v>
       </c>
       <c r="K96" s="3">
         <v>-169400</v>
@@ -3592,25 +3590,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-630400</v>
+        <v>-306400</v>
       </c>
       <c r="E100" s="3">
-        <v>-96500</v>
+        <v>-296100</v>
       </c>
       <c r="F100" s="3">
-        <v>-246900</v>
+        <v>-46800</v>
       </c>
       <c r="G100" s="3">
-        <v>-560200</v>
+        <v>-45400</v>
       </c>
       <c r="H100" s="3">
-        <v>-283800</v>
+        <v>-123600</v>
       </c>
       <c r="I100" s="3">
-        <v>-612500</v>
+        <v>-131400</v>
       </c>
       <c r="J100" s="3">
-        <v>-1022800</v>
+        <v>-292400</v>
       </c>
       <c r="K100" s="3">
         <v>-431000</v>
@@ -3627,25 +3625,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-5700</v>
+        <v>16500</v>
       </c>
       <c r="E101" s="3">
-        <v>-4600</v>
+        <v>17500</v>
       </c>
       <c r="F101" s="3">
-        <v>35000</v>
+        <v>9200</v>
       </c>
       <c r="G101" s="3">
-        <v>17700</v>
+        <v>8700</v>
       </c>
       <c r="H101" s="3">
-        <v>6100</v>
+        <v>3300</v>
       </c>
       <c r="I101" s="3">
-        <v>25400</v>
+        <v>3700</v>
       </c>
       <c r="J101" s="3">
-        <v>-5900</v>
+        <v>14100</v>
       </c>
       <c r="K101" s="3">
         <v>-34700</v>
@@ -3662,25 +3660,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>51300</v>
+        <v>24900</v>
       </c>
       <c r="E102" s="3">
-        <v>-1020000</v>
+        <v>24100</v>
       </c>
       <c r="F102" s="3">
-        <v>-11400</v>
+        <v>-494800</v>
       </c>
       <c r="G102" s="3">
-        <v>29200</v>
+        <v>-479700</v>
       </c>
       <c r="H102" s="3">
-        <v>449000</v>
+        <v>-5400</v>
       </c>
       <c r="I102" s="3">
-        <v>-278200</v>
+        <v>-5700</v>
       </c>
       <c r="J102" s="3">
-        <v>-67000</v>
+        <v>15200</v>
       </c>
       <c r="K102" s="3">
         <v>623500</v>

--- a/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>IMPUY</t>
   </si>
@@ -656,69 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -743,17 +750,23 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
         <v>3162900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2279000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -778,17 +791,23 @@
       <c r="J9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3">
         <v>1945800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1277500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -813,17 +832,23 @@
       <c r="J10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3">
         <v>1217200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1001500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +862,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +899,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +940,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -933,17 +972,23 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>-568000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>57300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -968,17 +1013,23 @@
       <c r="J15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,8 +1040,10 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1015,17 +1068,23 @@
       <c r="J17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3">
         <v>1227800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1370300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1050,17 +1109,23 @@
       <c r="J18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>1935200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>908700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,8 +1139,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1100,17 +1167,23 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>17800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>85600</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1135,17 +1208,23 @@
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>2096700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1021900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1170,17 +1249,23 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1205,17 +1290,23 @@
       <c r="J23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3">
         <v>1953000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>994300</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1240,17 +1331,23 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3">
         <v>569800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>285100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,8 +1381,14 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1310,17 +1413,23 @@
       <c r="J26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3">
         <v>1383200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>709200</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1345,17 +1454,23 @@
       <c r="J27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3">
         <v>1364700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>689300</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1504,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1415,17 +1536,23 @@
       <c r="J29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="K29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1586,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,8 +1627,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1520,17 +1659,23 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-17800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-85600</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1555,17 +1700,23 @@
       <c r="J33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3">
         <v>1364700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>689300</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,8 +1750,14 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1625,57 +1782,69 @@
       <c r="J35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3">
         <v>1364700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>689300</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1858,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,148 +1875,174 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>526800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>576400</v>
+      </c>
+      <c r="F41" s="3">
         <v>527500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>509700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>502300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>487000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1423900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1513900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1589500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1351600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>726300</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F42" s="3">
         <v>1900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>2100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>2100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>64100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>200</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>560600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>613400</v>
+      </c>
+      <c r="F43" s="3">
         <v>691100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>667900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>610900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>592300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>656700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>698200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>330600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>252500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>298300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1518200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1661400</v>
+      </c>
+      <c r="F44" s="3">
         <v>1455900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1406800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1477700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1432600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1291200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1372800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1585800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1167000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1059700</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1870,157 +2067,187 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>62600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>37000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2708100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2963400</v>
+      </c>
+      <c r="F46" s="3">
         <v>2771100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2677700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2806200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2720600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3597600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3825100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3773100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2833900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2121500</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>815400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>892300</v>
+      </c>
+      <c r="F47" s="3">
         <v>824400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>796600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>873400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>846800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>899800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>956700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1792100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>381900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>323600</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3477100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3804800</v>
+      </c>
+      <c r="F48" s="3">
         <v>3478600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3361300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3945300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3825000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3778800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4017800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3927000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3098000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2777100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>186600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>204200</v>
+      </c>
+      <c r="F49" s="3">
         <v>193000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>186500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>539600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>523100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>524000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>557100</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2281,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2322,55 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>16300</v>
+      </c>
+      <c r="F52" s="3">
         <v>16100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>15600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>184900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>179300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>192700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>204900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>207300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>213800</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2404,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7202100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7881000</v>
+      </c>
+      <c r="F54" s="3">
         <v>7283200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7037700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>8349500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>8094800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>8992900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>9561600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9699500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6527700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5222200</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2466,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,218 +2483,256 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>702400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>768600</v>
+      </c>
+      <c r="F57" s="3">
         <v>683800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>660800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>700700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>679300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>718400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>763900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>926700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>826700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>502300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>78300</v>
+        <v>102300</v>
       </c>
       <c r="E58" s="3">
-        <v>75600</v>
+        <v>112000</v>
       </c>
       <c r="F58" s="3">
         <v>78300</v>
       </c>
       <c r="G58" s="3">
+        <v>75600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>78300</v>
+      </c>
+      <c r="I58" s="3">
         <v>75900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>17800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>18900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>16000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>81300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>149900</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>73300</v>
+      </c>
+      <c r="F59" s="3">
         <v>39900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>38500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>53700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>52100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>77100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>82000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>139900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>130500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>28800</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>871600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>953800</v>
+      </c>
+      <c r="F60" s="3">
         <v>922700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>891600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>832700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>807300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>938200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>997600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1082600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1038500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>681000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>97200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>106300</v>
+      </c>
+      <c r="F61" s="3">
         <v>104700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>101200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>115200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>111700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>119700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>127300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>53300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>242700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>339600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>179800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>196800</v>
+      </c>
+      <c r="F62" s="3">
         <v>159700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>154400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>161000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>156100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>158300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>168300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>148500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>797700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>685100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2766,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2807,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2848,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1915900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2096500</v>
+      </c>
+      <c r="F66" s="3">
         <v>1990100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1923000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2136400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2071200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2301600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2447100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2294400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2212500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1851100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2910,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2947,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2988,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2691,11 +3026,17 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +3070,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2443400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2673800</v>
+      </c>
+      <c r="F72" s="3">
         <v>2425400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2343600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3457100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3351600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3938000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4187100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>5124200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2882200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1572000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +3152,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3193,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3234,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5002700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5474300</v>
+      </c>
+      <c r="F76" s="3">
         <v>5006800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4838000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5929500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5748600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6097400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6482900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7114900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4315200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3371100</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,48 +3316,60 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3005,17 +3394,23 @@
       <c r="J81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3">
         <v>1364700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>689300</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3424,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>112300</v>
+      </c>
+      <c r="F83" s="3">
         <v>107600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>114400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>108300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>102200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>91200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>102100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>88800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>143800</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3502,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3543,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3584,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3625,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3666,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>96200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>105200</v>
+      </c>
+      <c r="F89" s="3">
         <v>154200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>149000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>35900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>34800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>241100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>256400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>426000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1184600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>606700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3728,51 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-101200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-110800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-196700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-190100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-185800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-180100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-207900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-221100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-142300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2548000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2415000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3806,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3847,55 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-79600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-87100</v>
+      </c>
+      <c r="F94" s="3">
         <v>179900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>173900</v>
       </c>
-      <c r="F94" s="3">
-        <v>-481600</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-467000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-169200</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-164000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-139400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-148200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-127700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-95300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-76700</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,43 +3909,51 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>40600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>39400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>94800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>100800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>261600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-169400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3987,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +4028,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +4069,133 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-306400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-296100</v>
       </c>
-      <c r="F100" s="3">
-        <v>-46800</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-45400</v>
-      </c>
       <c r="H100" s="3">
+        <v>-359300</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-348300</v>
+      </c>
+      <c r="J100" s="3">
         <v>-123600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-131400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-292400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-431000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-168500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F101" s="3">
         <v>16500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>17500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>9200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>8700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>3300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>3700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>14100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-34700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>31200</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F102" s="3">
         <v>24900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>24100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-494800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-479700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-5700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>15200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>623500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>392700</v>
       </c>
-      <c r="M102" s="3" t="s">
+      <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMPUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>IMPUY</t>
   </si>
@@ -656,84 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -770,17 +777,23 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3">
         <v>3162900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2279000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -817,17 +830,23 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3">
         <v>1945800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1277500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,17 +883,23 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1217200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1001500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +917,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +966,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1019,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1024,17 +1063,23 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-568000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>57300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1071,17 +1116,23 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,8 +1147,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1134,17 +1187,23 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1227800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1370300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1181,17 +1240,23 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>1935200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>908700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1274,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1247,17 +1314,23 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>17800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>85600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1294,17 +1367,23 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>2096700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1021900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1341,17 +1420,23 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1388,17 +1473,23 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1953000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>994300</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1435,17 +1526,23 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3">
         <v>569800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>285100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,8 +1588,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1529,17 +1632,23 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3">
         <v>1383200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>709200</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1576,17 +1685,23 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3">
         <v>1364700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>689300</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1747,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1670,17 +1791,23 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1853,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1906,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1811,17 +1950,23 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-17800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-85600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1858,17 +2003,23 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3">
         <v>1364700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>689300</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,8 +2065,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1952,69 +2109,81 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3">
         <v>1364700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>689300</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2201,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,196 +2222,222 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>918700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>880600</v>
+      </c>
+      <c r="F41" s="3">
         <v>654900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>632900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>526800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>576400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>527500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>509700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>502300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>487000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1423900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1513900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1589500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1351600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>726300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F42" s="3">
         <v>2300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>2200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>2000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>2100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>64100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>200</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>751300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>720100</v>
+      </c>
+      <c r="F43" s="3">
         <v>634400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>613000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>560600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>613400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>691100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>667900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>610900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>592300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>656700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>698200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>330600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>252500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>298300</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2048400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1963500</v>
+      </c>
+      <c r="F44" s="3">
         <v>1674600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1618300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1518200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1661400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1455900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1406800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1477700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1432600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1291200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1372800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1585800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1167000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1059700</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2277,205 +2474,235 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>62600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>37000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3824600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3666000</v>
+      </c>
+      <c r="F46" s="3">
         <v>3034300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2932400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2708100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2963400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2771100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2677700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2806200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2720600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3597600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3825100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3773100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2833900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2121500</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>954000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>914400</v>
+      </c>
+      <c r="F47" s="3">
         <v>841100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>812800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>815400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>892300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>824400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>796600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>873400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>846800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>899800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>956700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1792100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>381900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>323600</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3601200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3451800</v>
+      </c>
+      <c r="F48" s="3">
         <v>3560700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3441100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3477100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3804800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3478600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3361300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3945300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3825000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3778800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4017800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3927000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3098000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2777100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>212800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>204000</v>
+      </c>
+      <c r="F49" s="3">
         <v>198400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>191700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>186600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>204200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>193000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>186500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>539600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>523100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>524000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>557100</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2748,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,55 +2801,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>16300</v>
+      </c>
+      <c r="F52" s="3">
         <v>16600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>16000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>14900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>16300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>16100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>15600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>184900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>179300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>192700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>204900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>207300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>213800</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2907,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8617200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8259900</v>
+      </c>
+      <c r="F54" s="3">
         <v>7651000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7394100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>7202100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7881000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>7283200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>7037700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>8349500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>8094800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>8992900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>9561600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9699500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>6527700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5222200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2985,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,290 +3006,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1048500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1005000</v>
+      </c>
+      <c r="F57" s="3">
         <v>674800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>652100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>702400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>768600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>607800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>587300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>700700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>679300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>718400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>763900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>926700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>826700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>502300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>86000</v>
+      </c>
+      <c r="F58" s="3">
         <v>121300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>117200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>102300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>112000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>78300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>75600</v>
       </c>
       <c r="J58" s="3">
         <v>78300</v>
       </c>
       <c r="K58" s="3">
+        <v>75600</v>
+      </c>
+      <c r="L58" s="3">
+        <v>78300</v>
+      </c>
+      <c r="M58" s="3">
         <v>75900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>17800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>18900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>16000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>81300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>149900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>167200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>160300</v>
+      </c>
+      <c r="F59" s="3">
         <v>85500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>82700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>66900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>73300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>39900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>38500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>53700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>52100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>77100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>82000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>139900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>130500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>28800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1305400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1251300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1105600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1068400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>871600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>953800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>922700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>891600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>832700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>807300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>938200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>997600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1082600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1038500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>681000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>88200</v>
+      </c>
+      <c r="F61" s="3">
         <v>92100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>89000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>97200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>106300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>104700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>101200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>115200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>111700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>119700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>127300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>53300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>242700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>339600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>292500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>280400</v>
+      </c>
+      <c r="F62" s="3">
         <v>247600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>239300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>179800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>196800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>159700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>154400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>161000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>156100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>158300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>168300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>148500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>797700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>685100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3373,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3426,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3479,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2459900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2357900</v>
+      </c>
+      <c r="F66" s="3">
         <v>2210000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2135800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1915900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2096500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1990100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1923000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2136400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2071200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2301600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2447100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2294400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2212500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1851100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3557,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3606,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3659,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3374,11 +3709,17 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3765,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3182100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3050100</v>
+      </c>
+      <c r="F72" s="3">
         <v>2531600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2446500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2443400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2673800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2425400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2343600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3457100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3351600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3938000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4187100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>5124200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2882200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1572000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3871,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3924,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3977,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5861100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5618100</v>
+      </c>
+      <c r="F76" s="3">
         <v>5156300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4983100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5002700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5474300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5006800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4838000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5929500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5748600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6097400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>6482900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>7114900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4315200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3371100</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,60 +4083,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3796,17 +4185,23 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3">
         <v>1364700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>689300</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4219,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>101100</v>
+      </c>
+      <c r="F83" s="3">
         <v>104200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>100700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>115800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>112300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>107600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>114400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>108300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>102200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>91200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>102100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>88800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>143800</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4321,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4374,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4427,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4480,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4533,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>295300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>283100</v>
+      </c>
+      <c r="F89" s="3">
         <v>105200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>101600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>96200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>105200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>154200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>149000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>35900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>34800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>241100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>256400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>426000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1184600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>606700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4611,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-88500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-84800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-85400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-82600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-101200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-110800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-196700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-190100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-185800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-180100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-207900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-221100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-142300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2548000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2415000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4713,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4766,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-84100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-80600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-57700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-55800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-79600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-87100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-133200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-128700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-169200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-164000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-139400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-148200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-127700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-95300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-76700</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,16 +4844,18 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E96" s="3">
+        <v>42800</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>4</v>
@@ -4396,38 +4863,44 @@
       <c r="G96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>40600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>39400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>94800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>100800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>261600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-169400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4946,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4999,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,145 +5052,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-94900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="F100" s="3">
         <v>12200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>11800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-17600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-19200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>6700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>6500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-359300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-348300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-123600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-131400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-292400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-431000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-168500</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-2800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>16500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>17500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>9200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>8700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>3300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>3700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>14100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-34700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>31200</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>108200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>103700</v>
+      </c>
+      <c r="F102" s="3">
         <v>56900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>55000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>24900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>24100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-494800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-479700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-5400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-5700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>15200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>623500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>392700</v>
       </c>
-      <c r="Q102" s="3" t="s">
+      <c r="S102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
